--- a/data.xlsx
+++ b/data.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="773" uniqueCount="485">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="729" uniqueCount="474">
   <si>
     <t>node_name_facebook</t>
   </si>
@@ -44,1372 +44,1339 @@
     <t>post_description</t>
   </si>
   <si>
-    <t>go 10023</t>
+    <t>go 10053</t>
+  </si>
+  <si>
+    <t>053.mp4</t>
+  </si>
+  <si>
+    <t>I am live, come see</t>
+  </si>
+  <si>
+    <t>Live broadcast is on air</t>
+  </si>
+  <si>
+    <t>go 10054</t>
+  </si>
+  <si>
+    <t>054.mp4</t>
+  </si>
+  <si>
+    <t>Live now, feel free to join</t>
+  </si>
+  <si>
+    <t>Live stream available now</t>
+  </si>
+  <si>
+    <t>go 10055</t>
+  </si>
+  <si>
+    <t>055.mp4</t>
+  </si>
+  <si>
+    <t>Going live, join me now</t>
+  </si>
+  <si>
+    <t>Chatting live with everyone</t>
+  </si>
+  <si>
+    <t>go 10057</t>
+  </si>
+  <si>
+    <t>057.mp4</t>
+  </si>
+  <si>
+    <t>Streaming live, welcome in</t>
+  </si>
+  <si>
+    <t>go 10058</t>
+  </si>
+  <si>
+    <t>058.mp4</t>
+  </si>
+  <si>
+    <t>I am live, come talk</t>
+  </si>
+  <si>
+    <t>Live session active now</t>
+  </si>
+  <si>
+    <t>go 10059</t>
+  </si>
+  <si>
+    <t>059.mp4</t>
+  </si>
+  <si>
+    <t>Live now, starting fresh</t>
+  </si>
+  <si>
+    <t>I am live, feel free to join</t>
+  </si>
+  <si>
+    <t>go 10060</t>
+  </si>
+  <si>
+    <t>060.mp4</t>
+  </si>
+  <si>
+    <t>Going live, welcome in</t>
+  </si>
+  <si>
+    <t>Live broadcast ongoing</t>
+  </si>
+  <si>
+    <t>go 10061</t>
+  </si>
+  <si>
+    <t>061.mp4</t>
+  </si>
+  <si>
+    <t>I am live, open chat</t>
+  </si>
+  <si>
+    <t>Live stream open now</t>
+  </si>
+  <si>
+    <t>go 10062</t>
+  </si>
+  <si>
+    <t>062.mp4</t>
+  </si>
+  <si>
+    <t>Live stream live now</t>
+  </si>
+  <si>
+    <t>Live now, say something</t>
+  </si>
+  <si>
+    <t>go 10063</t>
+  </si>
+  <si>
+    <t>063.mp4</t>
+  </si>
+  <si>
+    <t>I am live, see you inside</t>
+  </si>
+  <si>
+    <t>Streaming live, come inside</t>
+  </si>
+  <si>
+    <t>go 10064</t>
+  </si>
+  <si>
+    <t>064.mp4</t>
+  </si>
+  <si>
+    <t>Live now, join anytime</t>
+  </si>
+  <si>
+    <t>Live session started now</t>
+  </si>
+  <si>
+    <t>go 10065</t>
+  </si>
+  <si>
+    <t>065.mp4</t>
+  </si>
+  <si>
+    <t>Going live, everyone welcome</t>
+  </si>
+  <si>
+    <t>Live broadcast live</t>
+  </si>
+  <si>
+    <t>go 10066</t>
+  </si>
+  <si>
+    <t>066.mp4</t>
+  </si>
+  <si>
+    <t>I am live, don’t miss it</t>
+  </si>
+  <si>
+    <t>Live now, chatting</t>
+  </si>
+  <si>
+    <t>go 10067</t>
+  </si>
+  <si>
+    <t>067.mp4</t>
+  </si>
+  <si>
+    <t>Live broadcast happening</t>
+  </si>
+  <si>
+    <t>Streaming live, welcome</t>
+  </si>
+  <si>
+    <t>go 10068</t>
+  </si>
+  <si>
+    <t>068.mp4</t>
+  </si>
+  <si>
+    <t>I am live, come hang out</t>
+  </si>
+  <si>
+    <t>Live stream in progress</t>
+  </si>
+  <si>
+    <t>go 10069</t>
+  </si>
+  <si>
+    <t>069.mp4</t>
+  </si>
+  <si>
+    <t>Live now, just went live</t>
+  </si>
+  <si>
+    <t>This is my live stream</t>
+  </si>
+  <si>
+    <t>go 10070</t>
+  </si>
+  <si>
+    <t>070.mp4</t>
+  </si>
+  <si>
+    <t>Going live, let’s chat</t>
+  </si>
+  <si>
+    <t>I am live right now</t>
+  </si>
+  <si>
+    <t>go 10071</t>
+  </si>
+  <si>
+    <t>071.mp4</t>
+  </si>
+  <si>
+    <t>I am live now</t>
+  </si>
+  <si>
+    <t>Welcome to my live</t>
+  </si>
+  <si>
+    <t>go 10072</t>
+  </si>
+  <si>
+    <t>072.mp4</t>
+  </si>
+  <si>
+    <t>Going live right now</t>
+  </si>
+  <si>
+    <t>Join my live stream</t>
+  </si>
+  <si>
+    <t>go 10073</t>
+  </si>
+  <si>
+    <t>073.mp4</t>
+  </si>
+  <si>
+    <t>Live stream starting</t>
+  </si>
+  <si>
+    <t>This is a live broadcast</t>
+  </si>
+  <si>
+    <t>go 10074</t>
+  </si>
+  <si>
+    <t>074.mp4</t>
+  </si>
+  <si>
+    <t>I am live, join me</t>
+  </si>
+  <si>
+    <t>go 10075</t>
+  </si>
+  <si>
+    <t>075.mp4</t>
+  </si>
+  <si>
+    <t>Live now, come in</t>
+  </si>
+  <si>
+    <t>Hanging out live</t>
+  </si>
+  <si>
+    <t>go 10076</t>
+  </si>
+  <si>
+    <t>076.mp4</t>
+  </si>
+  <si>
+    <t>Starting my live stream</t>
+  </si>
+  <si>
+    <t>Chatting live right now</t>
+  </si>
+  <si>
+    <t>go 10077</t>
+  </si>
+  <si>
+    <t>077.mp4</t>
+  </si>
+  <si>
+    <t>I am live at the moment</t>
+  </si>
+  <si>
+    <t>Live stream, come in</t>
+  </si>
+  <si>
+    <t>go 10078</t>
+  </si>
+  <si>
+    <t>078.mp4</t>
+  </si>
+  <si>
+    <t>Live broadcast is on</t>
+  </si>
+  <si>
+    <t>This is my live session</t>
+  </si>
+  <si>
+    <t>go 10079</t>
+  </si>
+  <si>
+    <t>079.mp4</t>
+  </si>
+  <si>
+    <t>Live stream is open</t>
+  </si>
+  <si>
+    <t>Streaming live today</t>
+  </si>
+  <si>
+    <t>go 10080</t>
+  </si>
+  <si>
+    <t>080.mp4</t>
+  </si>
+  <si>
+    <t>I am live today</t>
+  </si>
+  <si>
+    <t>Live now, welcome everyone</t>
+  </si>
+  <si>
+    <t>go 10081</t>
+  </si>
+  <si>
+    <t>081.mp4</t>
+  </si>
+  <si>
+    <t>Live now, don’t miss it</t>
+  </si>
+  <si>
+    <t>Just going live</t>
+  </si>
+  <si>
+    <t>go 10082</t>
+  </si>
+  <si>
+    <t>082.mp4</t>
+  </si>
+  <si>
+    <t>Going live today</t>
+  </si>
+  <si>
+    <t>go 10083</t>
+  </si>
+  <si>
+    <t>083.mp4</t>
+  </si>
+  <si>
+    <t>Live stream is happening</t>
+  </si>
+  <si>
+    <t>Feel free to join the live</t>
+  </si>
+  <si>
+    <t>go 10084</t>
+  </si>
+  <si>
+    <t>084.mp4</t>
+  </si>
+  <si>
+    <t>I am live, say hi</t>
+  </si>
+  <si>
+    <t>Talking live right now</t>
+  </si>
+  <si>
+    <t>go 10085</t>
+  </si>
+  <si>
+    <t>085.mp4</t>
+  </si>
+  <si>
+    <t>Live now, welcome</t>
+  </si>
+  <si>
+    <t>Live broadcast, join anytime</t>
+  </si>
+  <si>
+    <t>go 10086</t>
+  </si>
+  <si>
+    <t>086.mp4</t>
+  </si>
+  <si>
+    <t>Live session started</t>
+  </si>
+  <si>
+    <t>This is my live room</t>
+  </si>
+  <si>
+    <t>go 10087</t>
+  </si>
+  <si>
+    <t>087.mp4</t>
+  </si>
+  <si>
+    <t>I am live, join the chat</t>
+  </si>
+  <si>
+    <t>Streaming live, say hi</t>
+  </si>
+  <si>
+    <t>go 10088</t>
+  </si>
+  <si>
+    <t>088.mp4</t>
+  </si>
+  <si>
+    <t>Live broadcast now</t>
+  </si>
+  <si>
+    <t>go 10089</t>
+  </si>
+  <si>
+    <t>089.mp4</t>
+  </si>
+  <si>
+    <t>Live stream online</t>
+  </si>
+  <si>
+    <t>go 10090</t>
+  </si>
+  <si>
+    <t>090.mp4</t>
+  </si>
+  <si>
+    <t>I am live right away</t>
+  </si>
+  <si>
+    <t>Live now, let’s chat</t>
+  </si>
+  <si>
+    <t>go 10091</t>
+  </si>
+  <si>
+    <t>091.mp4</t>
+  </si>
+  <si>
+    <t>Live now, come watch</t>
+  </si>
+  <si>
+    <t>Welcome to the live stream</t>
+  </si>
+  <si>
+    <t>go 10092</t>
+  </si>
+  <si>
+    <t>092.mp4</t>
+  </si>
+  <si>
+    <t>Going live, see you inside</t>
+  </si>
+  <si>
+    <t>Live session is active</t>
+  </si>
+  <si>
+    <t>go 10093</t>
+  </si>
+  <si>
+    <t>093.mp4</t>
+  </si>
+  <si>
+    <t>Live stream begins now</t>
+  </si>
+  <si>
+    <t>Just started the live</t>
+  </si>
+  <si>
+    <t>go 10094</t>
+  </si>
+  <si>
+    <t>094.mp4</t>
+  </si>
+  <si>
+    <t>Live now, come chat</t>
+  </si>
+  <si>
+    <t>go 10095</t>
+  </si>
+  <si>
+    <t>095.mp4</t>
+  </si>
+  <si>
+    <t>Live broadcast starting now</t>
+  </si>
+  <si>
+    <t>Streaming live at the moment</t>
+  </si>
+  <si>
+    <t>go 10096</t>
+  </si>
+  <si>
+    <t>096.mp4</t>
+  </si>
+  <si>
+    <t>I am live and waiting</t>
+  </si>
+  <si>
+    <t>Live broadcast is running</t>
+  </si>
+  <si>
+    <t>go 10097</t>
+  </si>
+  <si>
+    <t>097.mp4</t>
+  </si>
+  <si>
+    <t>Live now, everyone welcome</t>
+  </si>
+  <si>
+    <t>This is my live show</t>
+  </si>
+  <si>
+    <t>go 10098</t>
+  </si>
+  <si>
+    <t>098.mp4</t>
+  </si>
+  <si>
+    <t>Live stream is live</t>
+  </si>
+  <si>
+    <t>Live now, feel free to talk</t>
+  </si>
+  <si>
+    <t>go 10099</t>
+  </si>
+  <si>
+    <t>099.mp4</t>
+  </si>
+  <si>
+    <t>Welcome, I’m live</t>
+  </si>
+  <si>
+    <t>go 10100</t>
+  </si>
+  <si>
+    <t>100.mp4</t>
+  </si>
+  <si>
+    <t>Live now, just started</t>
+  </si>
+  <si>
+    <t>Live stream happening now</t>
+  </si>
+  <si>
+    <t>go 10101</t>
+  </si>
+  <si>
+    <t>101.mp4</t>
+  </si>
+  <si>
+    <t>Going live this moment</t>
+  </si>
+  <si>
+    <t>Live session just started</t>
+  </si>
+  <si>
+    <t>go 10102</t>
+  </si>
+  <si>
+    <t>102.mp4</t>
+  </si>
+  <si>
+    <t>I am live, come chat</t>
+  </si>
+  <si>
+    <t>I am live and chatting</t>
+  </si>
+  <si>
+    <t>go 10103</t>
+  </si>
+  <si>
+    <t>103.mp4</t>
+  </si>
+  <si>
+    <t>Live stream on air</t>
+  </si>
+  <si>
+    <t>Streaming live, come in</t>
+  </si>
+  <si>
+    <t>go 10104</t>
+  </si>
+  <si>
+    <t>104.mp4</t>
+  </si>
+  <si>
+    <t>Live broadcast is live</t>
+  </si>
+  <si>
+    <t>Live broadcast is open</t>
+  </si>
+  <si>
+    <t>go 10105</t>
+  </si>
+  <si>
+    <t>105.mp4</t>
+  </si>
+  <si>
+    <t>I am live, join anytime</t>
+  </si>
+  <si>
+    <t>Live now, come say hello</t>
+  </si>
+  <si>
+    <t>go 10106</t>
+  </si>
+  <si>
+    <t>106.mp4</t>
+  </si>
+  <si>
+    <t>Live now, take a look</t>
+  </si>
+  <si>
+    <t>This is my live channel</t>
+  </si>
+  <si>
+    <t>go 10107</t>
+  </si>
+  <si>
+    <t>107.mp4</t>
+  </si>
+  <si>
+    <t>Going live, don’t be late</t>
+  </si>
+  <si>
+    <t>Live stream is on</t>
+  </si>
+  <si>
+    <t>go 10108</t>
+  </si>
+  <si>
+    <t>108.mp4</t>
+  </si>
+  <si>
+    <t>I am live streaming now</t>
+  </si>
+  <si>
+    <t>Talking with viewers live</t>
+  </si>
+  <si>
+    <t>go 10109</t>
+  </si>
+  <si>
+    <t>109.mp4</t>
+  </si>
+  <si>
+    <t>Live stream is ready</t>
+  </si>
+  <si>
+    <t>Live now, welcome in</t>
+  </si>
+  <si>
+    <t>go 10110</t>
+  </si>
+  <si>
+    <t>110.mp4</t>
+  </si>
+  <si>
+    <t>I am live, come inside</t>
+  </si>
+  <si>
+    <t>Streaming live, join freely</t>
+  </si>
+  <si>
+    <t>go 10111</t>
+  </si>
+  <si>
+    <t>111.mp4</t>
+  </si>
+  <si>
+    <t>Live now, enjoy</t>
+  </si>
+  <si>
+    <t>Live session ongoing</t>
+  </si>
+  <si>
+    <t>go 10112</t>
+  </si>
+  <si>
+    <t>112.mp4</t>
+  </si>
+  <si>
+    <t>Going live right away</t>
+  </si>
+  <si>
+    <t>go 10113</t>
+  </si>
+  <si>
+    <t>113.mp4</t>
+  </si>
+  <si>
+    <t>I am live, say hello</t>
+  </si>
+  <si>
+    <t>Live broadcast active now</t>
+  </si>
+  <si>
+    <t>go 10114</t>
+  </si>
+  <si>
+    <t>114.mp4</t>
+  </si>
+  <si>
+    <t>Live stream just started</t>
+  </si>
+  <si>
+    <t>Chatting live, join me</t>
+  </si>
+  <si>
+    <t>go 10115</t>
+  </si>
+  <si>
+    <t>115.mp4</t>
+  </si>
+  <si>
+    <t>Live broadcast online</t>
+  </si>
+  <si>
+    <t>Live stream is available</t>
+  </si>
+  <si>
+    <t>go 10116</t>
+  </si>
+  <si>
+    <t>116.mp4</t>
+  </si>
+  <si>
+    <t>I am live now, welcome</t>
+  </si>
+  <si>
+    <t>Just went live</t>
+  </si>
+  <si>
+    <t>go 10117</t>
+  </si>
+  <si>
+    <t>117.mp4</t>
+  </si>
+  <si>
+    <t>Live now, come talk</t>
+  </si>
+  <si>
+    <t>go 10118</t>
+  </si>
+  <si>
+    <t>118.mp4</t>
+  </si>
+  <si>
+    <t>Going live, let’s go</t>
+  </si>
+  <si>
+    <t>go 10119</t>
+  </si>
+  <si>
+    <t>119.mp4</t>
+  </si>
+  <si>
+    <t>I am live, join freely</t>
+  </si>
+  <si>
+    <t>Live session is live</t>
+  </si>
+  <si>
+    <t>go 10120</t>
+  </si>
+  <si>
+    <t>120.mp4</t>
+  </si>
+  <si>
+    <t>Live stream is running</t>
+  </si>
+  <si>
+    <t>This is a live broadcast now</t>
+  </si>
+  <si>
+    <t>go 10121</t>
+  </si>
+  <si>
+    <t>121.mp4</t>
+  </si>
+  <si>
+    <t>I am live now, join me</t>
+  </si>
+  <si>
+    <t>Live now, welcome to join</t>
+  </si>
+  <si>
+    <t>go 10122</t>
+  </si>
+  <si>
+    <t>122.mp4</t>
+  </si>
+  <si>
+    <t>Live broadcast active</t>
+  </si>
+  <si>
+    <t>Streaming live, feel free</t>
+  </si>
+  <si>
+    <t>go 10123</t>
+  </si>
+  <si>
+    <t>123.mp4</t>
+  </si>
+  <si>
+    <t>I am live, waiting for you</t>
+  </si>
+  <si>
+    <t>Live broadcast happening now</t>
+  </si>
+  <si>
+    <t>go 10124</t>
+  </si>
+  <si>
+    <t>124.mp4</t>
+  </si>
+  <si>
+    <t>Live now, come check it out</t>
+  </si>
+  <si>
+    <t>Live session, join anytime</t>
+  </si>
+  <si>
+    <t>go 10125</t>
+  </si>
+  <si>
+    <t>125.mp4</t>
+  </si>
+  <si>
+    <t>Going live, join now</t>
+  </si>
+  <si>
+    <t>I am live and online</t>
+  </si>
+  <si>
+    <t>go 10127</t>
+  </si>
+  <si>
+    <t>127.mp4</t>
+  </si>
+  <si>
+    <t>Live stream is open now</t>
+  </si>
+  <si>
+    <t>Chatting live, say hi</t>
+  </si>
+  <si>
+    <t>go 10128</t>
+  </si>
+  <si>
+    <t>128.mp4</t>
+  </si>
+  <si>
+    <t>I am live, welcome everyone</t>
+  </si>
+  <si>
+    <t>Live now, open chat</t>
+  </si>
+  <si>
+    <t>go 10129</t>
+  </si>
+  <si>
+    <t>129.mp4</t>
+  </si>
+  <si>
+    <t>Streaming live, come chat</t>
+  </si>
+  <si>
+    <t>go 10130</t>
+  </si>
+  <si>
+    <t>130.mp4</t>
+  </si>
+  <si>
+    <t>Going live, starting now</t>
+  </si>
+  <si>
+    <t>Live broadcast is live now</t>
+  </si>
+  <si>
+    <t>go 10131</t>
+  </si>
+  <si>
+    <t>001.mp4</t>
+  </si>
+  <si>
+    <t>I am live, don’t miss out</t>
+  </si>
+  <si>
+    <t>Live session is open</t>
+  </si>
+  <si>
+    <t>go 10132</t>
+  </si>
+  <si>
+    <t>002.mp4</t>
+  </si>
+  <si>
+    <t>Live stream is happening now</t>
+  </si>
+  <si>
+    <t>Live now, talk with me</t>
+  </si>
+  <si>
+    <t>go 10133</t>
+  </si>
+  <si>
+    <t>003.mp4</t>
+  </si>
+  <si>
+    <t>I am live, come watch</t>
+  </si>
+  <si>
+    <t>Streaming live right away</t>
+  </si>
+  <si>
+    <t>go 10134</t>
+  </si>
+  <si>
+    <t>004.mp4</t>
+  </si>
+  <si>
+    <t>Live broadcast just began</t>
+  </si>
+  <si>
+    <t>Live stream started</t>
+  </si>
+  <si>
+    <t>go 10135</t>
+  </si>
+  <si>
+    <t>005.mp4</t>
+  </si>
+  <si>
+    <t>I am live, come say hi</t>
+  </si>
+  <si>
+    <t>go 10136</t>
+  </si>
+  <si>
+    <t>006.mp4</t>
+  </si>
+  <si>
+    <t>Live now, all welcome</t>
+  </si>
+  <si>
+    <t>I am live, welcome</t>
+  </si>
+  <si>
+    <t>go 10137</t>
+  </si>
+  <si>
+    <t>007.mp4</t>
+  </si>
+  <si>
+    <t>Going live, hop in</t>
+  </si>
+  <si>
+    <t>Live session in progress</t>
+  </si>
+  <si>
+    <t>go 10138</t>
+  </si>
+  <si>
+    <t>008.mp4</t>
+  </si>
+  <si>
+    <t>I am live, join the fun</t>
+  </si>
+  <si>
+    <t>Streaming live, join now</t>
+  </si>
+  <si>
+    <t>go 10139</t>
+  </si>
+  <si>
+    <t>009.mp4</t>
+  </si>
+  <si>
+    <t>Live stream is live now</t>
+  </si>
+  <si>
+    <t>Live now, feel free to comment</t>
+  </si>
+  <si>
+    <t>go 10140</t>
+  </si>
+  <si>
+    <t>010.mp4</t>
+  </si>
+  <si>
+    <t>go 10141</t>
+  </si>
+  <si>
+    <t>011.mp4</t>
+  </si>
+  <si>
+    <t>go 10142</t>
+  </si>
+  <si>
+    <t>012.mp4</t>
+  </si>
+  <si>
+    <t>go 10143</t>
+  </si>
+  <si>
+    <t>013.mp4</t>
+  </si>
+  <si>
+    <t>I am live, ready to chat</t>
+  </si>
+  <si>
+    <t>Live now, come hang out</t>
+  </si>
+  <si>
+    <t>go 10144</t>
+  </si>
+  <si>
+    <t>014.mp4</t>
+  </si>
+  <si>
+    <t>go 10145</t>
+  </si>
+  <si>
+    <t>015.mp4</t>
+  </si>
+  <si>
+    <t>go 10148</t>
+  </si>
+  <si>
+    <t>018.mp4</t>
+  </si>
+  <si>
+    <t>go 10149</t>
+  </si>
+  <si>
+    <t>019.mp4</t>
+  </si>
+  <si>
+    <t>go 10150</t>
+  </si>
+  <si>
+    <t>020.mp4</t>
+  </si>
+  <si>
+    <t>go 10151</t>
+  </si>
+  <si>
+    <t>021.mp4</t>
+  </si>
+  <si>
+    <t>go 10152</t>
+  </si>
+  <si>
+    <t>022.mp4</t>
+  </si>
+  <si>
+    <t>go 10153</t>
   </si>
   <si>
     <t>023.mp4</t>
   </si>
   <si>
-    <t>I am live, come inside</t>
-  </si>
-  <si>
-    <t>Streaming live, join freely</t>
-  </si>
-  <si>
-    <t>go 10027</t>
+    <t>go 10154</t>
+  </si>
+  <si>
+    <t>024.mp4</t>
+  </si>
+  <si>
+    <t>go 10155</t>
+  </si>
+  <si>
+    <t>025.mp4</t>
+  </si>
+  <si>
+    <t>go 10156</t>
+  </si>
+  <si>
+    <t>026.mp4</t>
+  </si>
+  <si>
+    <t>go 10157</t>
   </si>
   <si>
     <t>027.mp4</t>
   </si>
   <si>
-    <t>Live stream just started</t>
-  </si>
-  <si>
-    <t>Chatting live, join me</t>
-  </si>
-  <si>
-    <t>go 10028</t>
+    <t>go 10158</t>
   </si>
   <si>
     <t>028.mp4</t>
   </si>
   <si>
-    <t>Live broadcast online</t>
-  </si>
-  <si>
-    <t>Live stream is available</t>
-  </si>
-  <si>
-    <t>go 10031</t>
+    <t>go 10159</t>
+  </si>
+  <si>
+    <t>029.mp4</t>
+  </si>
+  <si>
+    <t>go 10160</t>
+  </si>
+  <si>
+    <t>030.mp4</t>
+  </si>
+  <si>
+    <t>go 10161</t>
   </si>
   <si>
     <t>031.mp4</t>
   </si>
   <si>
-    <t>Going live, let’s go</t>
-  </si>
-  <si>
-    <t>Streaming live today</t>
-  </si>
-  <si>
-    <t>go 10032</t>
+    <t>go 10162</t>
   </si>
   <si>
     <t>032.mp4</t>
   </si>
   <si>
-    <t>I am live, join freely</t>
-  </si>
-  <si>
-    <t>Live session is live</t>
-  </si>
-  <si>
-    <t>go 10033</t>
+    <t>go 10163</t>
   </si>
   <si>
     <t>033.mp4</t>
   </si>
   <si>
-    <t>Live stream is running</t>
-  </si>
-  <si>
-    <t>This is a live broadcast now</t>
-  </si>
-  <si>
-    <t>go 10039</t>
+    <t>go 10164</t>
+  </si>
+  <si>
+    <t>034.mp4</t>
+  </si>
+  <si>
+    <t>go 10165</t>
+  </si>
+  <si>
+    <t>035.mp4</t>
+  </si>
+  <si>
+    <t>go 10166</t>
+  </si>
+  <si>
+    <t>036.mp4</t>
+  </si>
+  <si>
+    <t>go 10167</t>
+  </si>
+  <si>
+    <t>037.mp4</t>
+  </si>
+  <si>
+    <t>go 10168</t>
+  </si>
+  <si>
+    <t>038.mp4</t>
+  </si>
+  <si>
+    <t>go 10169</t>
   </si>
   <si>
     <t>039.mp4</t>
   </si>
   <si>
+    <t>go 10170</t>
+  </si>
+  <si>
+    <t>040.mp4</t>
+  </si>
+  <si>
+    <t>go 10171</t>
+  </si>
+  <si>
+    <t>041.mp4</t>
+  </si>
+  <si>
+    <t>go 10172</t>
+  </si>
+  <si>
+    <t>042.mp4</t>
+  </si>
+  <si>
+    <t>go 10173</t>
+  </si>
+  <si>
+    <t>043.mp4</t>
+  </si>
+  <si>
+    <t>go 10174</t>
+  </si>
+  <si>
+    <t>044.mp4</t>
+  </si>
+  <si>
+    <t>go 10175</t>
+  </si>
+  <si>
+    <t>045.mp4</t>
+  </si>
+  <si>
+    <t>go 10176</t>
+  </si>
+  <si>
+    <t>046.mp4</t>
+  </si>
+  <si>
+    <t>go 10177</t>
+  </si>
+  <si>
+    <t>047.mp4</t>
+  </si>
+  <si>
+    <t>go 10178</t>
+  </si>
+  <si>
+    <t>048.mp4</t>
+  </si>
+  <si>
+    <t>go 10179</t>
+  </si>
+  <si>
+    <t>049.mp4</t>
+  </si>
+  <si>
+    <t>go 10180</t>
+  </si>
+  <si>
+    <t>050.mp4</t>
+  </si>
+  <si>
+    <t>go 10181</t>
+  </si>
+  <si>
+    <t>051.mp4</t>
+  </si>
+  <si>
+    <t>go 10182</t>
+  </si>
+  <si>
+    <t>052.mp4</t>
+  </si>
+  <si>
+    <t>go 10183</t>
+  </si>
+  <si>
+    <t>go 10184</t>
+  </si>
+  <si>
+    <t>go 10185</t>
+  </si>
+  <si>
+    <t>go 10186</t>
+  </si>
+  <si>
+    <t>056.mp4</t>
+  </si>
+  <si>
+    <t>go 10187</t>
+  </si>
+  <si>
+    <t>go 10188</t>
+  </si>
+  <si>
+    <t>go 10189</t>
+  </si>
+  <si>
+    <t>go 10190</t>
+  </si>
+  <si>
+    <t>go 10191</t>
+  </si>
+  <si>
+    <t>go 10192</t>
+  </si>
+  <si>
+    <t>go 10193</t>
+  </si>
+  <si>
+    <t>go 10194</t>
+  </si>
+  <si>
+    <t>go 10195</t>
+  </si>
+  <si>
+    <t>go 10196</t>
+  </si>
+  <si>
+    <t>go 10197</t>
+  </si>
+  <si>
+    <t>go 10198</t>
+  </si>
+  <si>
+    <t>go 10199</t>
+  </si>
+  <si>
+    <t>go 10200</t>
+  </si>
+  <si>
+    <t>go 10201</t>
+  </si>
+  <si>
+    <t>go 10202</t>
+  </si>
+  <si>
+    <t>go 10203</t>
+  </si>
+  <si>
+    <t>go 10204</t>
+  </si>
+  <si>
+    <t>go 10205</t>
+  </si>
+  <si>
+    <t>go 10206</t>
+  </si>
+  <si>
+    <t>go 10207</t>
+  </si>
+  <si>
+    <t>go 10208</t>
+  </si>
+  <si>
+    <t>go 10209</t>
+  </si>
+  <si>
+    <t>go 10210</t>
+  </si>
+  <si>
+    <t>go 10211</t>
+  </si>
+  <si>
+    <t>go 10212</t>
+  </si>
+  <si>
+    <t>go 10213</t>
+  </si>
+  <si>
     <t>I am live, feel free to come</t>
-  </si>
-  <si>
-    <t>go 10042</t>
-  </si>
-  <si>
-    <t>042.mp4</t>
-  </si>
-  <si>
-    <t>Live now, say something</t>
-  </si>
-  <si>
-    <t>Streaming live, come chat</t>
-  </si>
-  <si>
-    <t>go 10043</t>
-  </si>
-  <si>
-    <t>043.mp4</t>
-  </si>
-  <si>
-    <t>Going live, starting now</t>
-  </si>
-  <si>
-    <t>Live broadcast is live now</t>
-  </si>
-  <si>
-    <t>go 10045</t>
-  </si>
-  <si>
-    <t>045.mp4</t>
-  </si>
-  <si>
-    <t>Live stream is happening now</t>
-  </si>
-  <si>
-    <t>Live now, talk with me</t>
-  </si>
-  <si>
-    <t>go 10047</t>
-  </si>
-  <si>
-    <t>047.mp4</t>
-  </si>
-  <si>
-    <t>Live broadcast just began</t>
-  </si>
-  <si>
-    <t>Live stream started</t>
-  </si>
-  <si>
-    <t>go 10053</t>
-  </si>
-  <si>
-    <t>053.mp4</t>
-  </si>
-  <si>
-    <t>I am live, come see</t>
-  </si>
-  <si>
-    <t>Live broadcast is on air</t>
-  </si>
-  <si>
-    <t>go 10054</t>
-  </si>
-  <si>
-    <t>054.mp4</t>
-  </si>
-  <si>
-    <t>Live now, feel free to join</t>
-  </si>
-  <si>
-    <t>Live stream available now</t>
-  </si>
-  <si>
-    <t>go 10055</t>
-  </si>
-  <si>
-    <t>055.mp4</t>
-  </si>
-  <si>
-    <t>Going live, join me now</t>
-  </si>
-  <si>
-    <t>Chatting live with everyone</t>
-  </si>
-  <si>
-    <t>go 10057</t>
-  </si>
-  <si>
-    <t>057.mp4</t>
-  </si>
-  <si>
-    <t>Streaming live, welcome in</t>
-  </si>
-  <si>
-    <t>go 10058</t>
-  </si>
-  <si>
-    <t>058.mp4</t>
-  </si>
-  <si>
-    <t>I am live, come talk</t>
-  </si>
-  <si>
-    <t>Live session active now</t>
-  </si>
-  <si>
-    <t>go 10059</t>
-  </si>
-  <si>
-    <t>059.mp4</t>
-  </si>
-  <si>
-    <t>Live now, starting fresh</t>
-  </si>
-  <si>
-    <t>I am live, feel free to join</t>
-  </si>
-  <si>
-    <t>go 10060</t>
-  </si>
-  <si>
-    <t>060.mp4</t>
-  </si>
-  <si>
-    <t>Going live, welcome in</t>
-  </si>
-  <si>
-    <t>Live broadcast ongoing</t>
-  </si>
-  <si>
-    <t>go 10061</t>
-  </si>
-  <si>
-    <t>061.mp4</t>
-  </si>
-  <si>
-    <t>I am live, open chat</t>
-  </si>
-  <si>
-    <t>Live stream open now</t>
-  </si>
-  <si>
-    <t>go 10062</t>
-  </si>
-  <si>
-    <t>062.mp4</t>
-  </si>
-  <si>
-    <t>Live stream live now</t>
-  </si>
-  <si>
-    <t>go 10063</t>
-  </si>
-  <si>
-    <t>063.mp4</t>
-  </si>
-  <si>
-    <t>I am live, see you inside</t>
-  </si>
-  <si>
-    <t>Streaming live, come inside</t>
-  </si>
-  <si>
-    <t>go 10064</t>
-  </si>
-  <si>
-    <t>064.mp4</t>
-  </si>
-  <si>
-    <t>Live now, join anytime</t>
-  </si>
-  <si>
-    <t>Live session started now</t>
-  </si>
-  <si>
-    <t>go 10065</t>
-  </si>
-  <si>
-    <t>065.mp4</t>
-  </si>
-  <si>
-    <t>Going live, everyone welcome</t>
-  </si>
-  <si>
-    <t>Live broadcast live</t>
-  </si>
-  <si>
-    <t>go 10066</t>
-  </si>
-  <si>
-    <t>066.mp4</t>
-  </si>
-  <si>
-    <t>I am live, don’t miss it</t>
-  </si>
-  <si>
-    <t>Live now, chatting</t>
-  </si>
-  <si>
-    <t>go 10067</t>
-  </si>
-  <si>
-    <t>067.mp4</t>
-  </si>
-  <si>
-    <t>Live broadcast happening</t>
-  </si>
-  <si>
-    <t>Streaming live, welcome</t>
-  </si>
-  <si>
-    <t>go 10068</t>
-  </si>
-  <si>
-    <t>068.mp4</t>
-  </si>
-  <si>
-    <t>I am live, come hang out</t>
-  </si>
-  <si>
-    <t>Live stream in progress</t>
-  </si>
-  <si>
-    <t>go 10069</t>
-  </si>
-  <si>
-    <t>069.mp4</t>
-  </si>
-  <si>
-    <t>Live now, just went live</t>
-  </si>
-  <si>
-    <t>This is my live stream</t>
-  </si>
-  <si>
-    <t>go 10070</t>
-  </si>
-  <si>
-    <t>070.mp4</t>
-  </si>
-  <si>
-    <t>Going live, let’s chat</t>
-  </si>
-  <si>
-    <t>I am live right now</t>
-  </si>
-  <si>
-    <t>go 10071</t>
-  </si>
-  <si>
-    <t>071.mp4</t>
-  </si>
-  <si>
-    <t>I am live now</t>
-  </si>
-  <si>
-    <t>Welcome to my live</t>
-  </si>
-  <si>
-    <t>go 10072</t>
-  </si>
-  <si>
-    <t>072.mp4</t>
-  </si>
-  <si>
-    <t>Going live right now</t>
-  </si>
-  <si>
-    <t>Join my live stream</t>
-  </si>
-  <si>
-    <t>go 10073</t>
-  </si>
-  <si>
-    <t>073.mp4</t>
-  </si>
-  <si>
-    <t>Live stream starting</t>
-  </si>
-  <si>
-    <t>This is a live broadcast</t>
-  </si>
-  <si>
-    <t>go 10074</t>
-  </si>
-  <si>
-    <t>074.mp4</t>
-  </si>
-  <si>
-    <t>I am live, join me</t>
-  </si>
-  <si>
-    <t>go 10075</t>
-  </si>
-  <si>
-    <t>075.mp4</t>
-  </si>
-  <si>
-    <t>Live now, come in</t>
-  </si>
-  <si>
-    <t>Hanging out live</t>
-  </si>
-  <si>
-    <t>go 10076</t>
-  </si>
-  <si>
-    <t>076.mp4</t>
-  </si>
-  <si>
-    <t>Starting my live stream</t>
-  </si>
-  <si>
-    <t>Chatting live right now</t>
-  </si>
-  <si>
-    <t>go 10077</t>
-  </si>
-  <si>
-    <t>077.mp4</t>
-  </si>
-  <si>
-    <t>I am live at the moment</t>
-  </si>
-  <si>
-    <t>Live stream, come in</t>
-  </si>
-  <si>
-    <t>go 10078</t>
-  </si>
-  <si>
-    <t>078.mp4</t>
-  </si>
-  <si>
-    <t>Live broadcast is on</t>
-  </si>
-  <si>
-    <t>This is my live session</t>
-  </si>
-  <si>
-    <t>go 10079</t>
-  </si>
-  <si>
-    <t>079.mp4</t>
-  </si>
-  <si>
-    <t>Live stream is open</t>
-  </si>
-  <si>
-    <t>go 10080</t>
-  </si>
-  <si>
-    <t>080.mp4</t>
-  </si>
-  <si>
-    <t>I am live today</t>
-  </si>
-  <si>
-    <t>Live now, welcome everyone</t>
-  </si>
-  <si>
-    <t>go 10081</t>
-  </si>
-  <si>
-    <t>081.mp4</t>
-  </si>
-  <si>
-    <t>Live now, don’t miss it</t>
-  </si>
-  <si>
-    <t>Just going live</t>
-  </si>
-  <si>
-    <t>go 10082</t>
-  </si>
-  <si>
-    <t>082.mp4</t>
-  </si>
-  <si>
-    <t>Going live today</t>
-  </si>
-  <si>
-    <t>go 10083</t>
-  </si>
-  <si>
-    <t>083.mp4</t>
-  </si>
-  <si>
-    <t>Live stream is happening</t>
-  </si>
-  <si>
-    <t>Feel free to join the live</t>
-  </si>
-  <si>
-    <t>go 10084</t>
-  </si>
-  <si>
-    <t>084.mp4</t>
-  </si>
-  <si>
-    <t>I am live, say hi</t>
-  </si>
-  <si>
-    <t>Talking live right now</t>
-  </si>
-  <si>
-    <t>go 10085</t>
-  </si>
-  <si>
-    <t>085.mp4</t>
-  </si>
-  <si>
-    <t>Live now, welcome</t>
-  </si>
-  <si>
-    <t>Live broadcast, join anytime</t>
-  </si>
-  <si>
-    <t>go 10086</t>
-  </si>
-  <si>
-    <t>086.mp4</t>
-  </si>
-  <si>
-    <t>Live session started</t>
-  </si>
-  <si>
-    <t>This is my live room</t>
-  </si>
-  <si>
-    <t>go 10087</t>
-  </si>
-  <si>
-    <t>087.mp4</t>
-  </si>
-  <si>
-    <t>I am live, join the chat</t>
-  </si>
-  <si>
-    <t>Streaming live, say hi</t>
-  </si>
-  <si>
-    <t>go 10088</t>
-  </si>
-  <si>
-    <t>088.mp4</t>
-  </si>
-  <si>
-    <t>Live broadcast now</t>
-  </si>
-  <si>
-    <t>go 10089</t>
-  </si>
-  <si>
-    <t>089.mp4</t>
-  </si>
-  <si>
-    <t>Live stream online</t>
-  </si>
-  <si>
-    <t>go 10090</t>
-  </si>
-  <si>
-    <t>090.mp4</t>
-  </si>
-  <si>
-    <t>I am live right away</t>
-  </si>
-  <si>
-    <t>Live now, let’s chat</t>
-  </si>
-  <si>
-    <t>go 10091</t>
-  </si>
-  <si>
-    <t>091.mp4</t>
-  </si>
-  <si>
-    <t>Live now, come watch</t>
-  </si>
-  <si>
-    <t>Welcome to the live stream</t>
-  </si>
-  <si>
-    <t>go 10092</t>
-  </si>
-  <si>
-    <t>092.mp4</t>
-  </si>
-  <si>
-    <t>Going live, see you inside</t>
-  </si>
-  <si>
-    <t>Live session is active</t>
-  </si>
-  <si>
-    <t>go 10093</t>
-  </si>
-  <si>
-    <t>093.mp4</t>
-  </si>
-  <si>
-    <t>Live stream begins now</t>
-  </si>
-  <si>
-    <t>Just started the live</t>
-  </si>
-  <si>
-    <t>go 10094</t>
-  </si>
-  <si>
-    <t>094.mp4</t>
-  </si>
-  <si>
-    <t>Live now, come chat</t>
-  </si>
-  <si>
-    <t>go 10095</t>
-  </si>
-  <si>
-    <t>095.mp4</t>
-  </si>
-  <si>
-    <t>Live broadcast starting now</t>
-  </si>
-  <si>
-    <t>Streaming live at the moment</t>
-  </si>
-  <si>
-    <t>go 10096</t>
-  </si>
-  <si>
-    <t>096.mp4</t>
-  </si>
-  <si>
-    <t>I am live and waiting</t>
-  </si>
-  <si>
-    <t>Live broadcast is running</t>
-  </si>
-  <si>
-    <t>go 10097</t>
-  </si>
-  <si>
-    <t>097.mp4</t>
-  </si>
-  <si>
-    <t>Live now, everyone welcome</t>
-  </si>
-  <si>
-    <t>This is my live show</t>
-  </si>
-  <si>
-    <t>go 10098</t>
-  </si>
-  <si>
-    <t>098.mp4</t>
-  </si>
-  <si>
-    <t>Live stream is live</t>
-  </si>
-  <si>
-    <t>Live now, feel free to talk</t>
-  </si>
-  <si>
-    <t>go 10099</t>
-  </si>
-  <si>
-    <t>099.mp4</t>
-  </si>
-  <si>
-    <t>Welcome, I’m live</t>
-  </si>
-  <si>
-    <t>go 10100</t>
-  </si>
-  <si>
-    <t>100.mp4</t>
-  </si>
-  <si>
-    <t>Live now, just started</t>
-  </si>
-  <si>
-    <t>Live stream happening now</t>
-  </si>
-  <si>
-    <t>go 10101</t>
-  </si>
-  <si>
-    <t>101.mp4</t>
-  </si>
-  <si>
-    <t>Going live this moment</t>
-  </si>
-  <si>
-    <t>Live session just started</t>
-  </si>
-  <si>
-    <t>go 10102</t>
-  </si>
-  <si>
-    <t>102.mp4</t>
-  </si>
-  <si>
-    <t>I am live, come chat</t>
-  </si>
-  <si>
-    <t>I am live and chatting</t>
-  </si>
-  <si>
-    <t>go 10103</t>
-  </si>
-  <si>
-    <t>103.mp4</t>
-  </si>
-  <si>
-    <t>Live stream on air</t>
-  </si>
-  <si>
-    <t>Streaming live, come in</t>
-  </si>
-  <si>
-    <t>go 10104</t>
-  </si>
-  <si>
-    <t>104.mp4</t>
-  </si>
-  <si>
-    <t>Live broadcast is live</t>
-  </si>
-  <si>
-    <t>Live broadcast is open</t>
-  </si>
-  <si>
-    <t>go 10105</t>
-  </si>
-  <si>
-    <t>105.mp4</t>
-  </si>
-  <si>
-    <t>I am live, join anytime</t>
-  </si>
-  <si>
-    <t>Live now, come say hello</t>
-  </si>
-  <si>
-    <t>go 10106</t>
-  </si>
-  <si>
-    <t>106.mp4</t>
-  </si>
-  <si>
-    <t>Live now, take a look</t>
-  </si>
-  <si>
-    <t>This is my live channel</t>
-  </si>
-  <si>
-    <t>go 10107</t>
-  </si>
-  <si>
-    <t>107.mp4</t>
-  </si>
-  <si>
-    <t>Going live, don’t be late</t>
-  </si>
-  <si>
-    <t>Live stream is on</t>
-  </si>
-  <si>
-    <t>go 10108</t>
-  </si>
-  <si>
-    <t>108.mp4</t>
-  </si>
-  <si>
-    <t>I am live streaming now</t>
-  </si>
-  <si>
-    <t>Talking with viewers live</t>
-  </si>
-  <si>
-    <t>go 10109</t>
-  </si>
-  <si>
-    <t>109.mp4</t>
-  </si>
-  <si>
-    <t>Live stream is ready</t>
-  </si>
-  <si>
-    <t>Live now, welcome in</t>
-  </si>
-  <si>
-    <t>go 10110</t>
-  </si>
-  <si>
-    <t>110.mp4</t>
-  </si>
-  <si>
-    <t>go 10111</t>
-  </si>
-  <si>
-    <t>111.mp4</t>
-  </si>
-  <si>
-    <t>Live now, enjoy</t>
-  </si>
-  <si>
-    <t>Live session ongoing</t>
-  </si>
-  <si>
-    <t>go 10112</t>
-  </si>
-  <si>
-    <t>112.mp4</t>
-  </si>
-  <si>
-    <t>Going live right away</t>
-  </si>
-  <si>
-    <t>go 10113</t>
-  </si>
-  <si>
-    <t>113.mp4</t>
-  </si>
-  <si>
-    <t>I am live, say hello</t>
-  </si>
-  <si>
-    <t>Live broadcast active now</t>
-  </si>
-  <si>
-    <t>go 10114</t>
-  </si>
-  <si>
-    <t>114.mp4</t>
-  </si>
-  <si>
-    <t>go 10115</t>
-  </si>
-  <si>
-    <t>115.mp4</t>
-  </si>
-  <si>
-    <t>go 10116</t>
-  </si>
-  <si>
-    <t>116.mp4</t>
-  </si>
-  <si>
-    <t>I am live now, welcome</t>
-  </si>
-  <si>
-    <t>Just went live</t>
-  </si>
-  <si>
-    <t>go 10117</t>
-  </si>
-  <si>
-    <t>117.mp4</t>
-  </si>
-  <si>
-    <t>Live now, come talk</t>
-  </si>
-  <si>
-    <t>go 10118</t>
-  </si>
-  <si>
-    <t>118.mp4</t>
-  </si>
-  <si>
-    <t>go 10119</t>
-  </si>
-  <si>
-    <t>119.mp4</t>
-  </si>
-  <si>
-    <t>go 10120</t>
-  </si>
-  <si>
-    <t>120.mp4</t>
-  </si>
-  <si>
-    <t>go 10121</t>
-  </si>
-  <si>
-    <t>121.mp4</t>
-  </si>
-  <si>
-    <t>I am live now, join me</t>
-  </si>
-  <si>
-    <t>Live now, welcome to join</t>
-  </si>
-  <si>
-    <t>go 10122</t>
-  </si>
-  <si>
-    <t>122.mp4</t>
-  </si>
-  <si>
-    <t>Live broadcast active</t>
-  </si>
-  <si>
-    <t>Streaming live, feel free</t>
-  </si>
-  <si>
-    <t>go 10123</t>
-  </si>
-  <si>
-    <t>123.mp4</t>
-  </si>
-  <si>
-    <t>I am live, waiting for you</t>
-  </si>
-  <si>
-    <t>Live broadcast happening now</t>
-  </si>
-  <si>
-    <t>go 10124</t>
-  </si>
-  <si>
-    <t>124.mp4</t>
-  </si>
-  <si>
-    <t>Live now, come check it out</t>
-  </si>
-  <si>
-    <t>Live session, join anytime</t>
-  </si>
-  <si>
-    <t>go 10125</t>
-  </si>
-  <si>
-    <t>125.mp4</t>
-  </si>
-  <si>
-    <t>Going live, join now</t>
-  </si>
-  <si>
-    <t>I am live and online</t>
-  </si>
-  <si>
-    <t>go 10127</t>
-  </si>
-  <si>
-    <t>127.mp4</t>
-  </si>
-  <si>
-    <t>Live stream is open now</t>
-  </si>
-  <si>
-    <t>Chatting live, say hi</t>
-  </si>
-  <si>
-    <t>go 10128</t>
-  </si>
-  <si>
-    <t>128.mp4</t>
-  </si>
-  <si>
-    <t>I am live, welcome everyone</t>
-  </si>
-  <si>
-    <t>Live now, open chat</t>
-  </si>
-  <si>
-    <t>go 10129</t>
-  </si>
-  <si>
-    <t>129.mp4</t>
-  </si>
-  <si>
-    <t>go 10130</t>
-  </si>
-  <si>
-    <t>130.mp4</t>
-  </si>
-  <si>
-    <t>go 10131</t>
-  </si>
-  <si>
-    <t>001.mp4</t>
-  </si>
-  <si>
-    <t>I am live, don’t miss out</t>
-  </si>
-  <si>
-    <t>Live session is open</t>
-  </si>
-  <si>
-    <t>go 10132</t>
-  </si>
-  <si>
-    <t>002.mp4</t>
-  </si>
-  <si>
-    <t>go 10133</t>
-  </si>
-  <si>
-    <t>003.mp4</t>
-  </si>
-  <si>
-    <t>I am live, come watch</t>
-  </si>
-  <si>
-    <t>Streaming live right away</t>
-  </si>
-  <si>
-    <t>go 10134</t>
-  </si>
-  <si>
-    <t>004.mp4</t>
-  </si>
-  <si>
-    <t>go 10135</t>
-  </si>
-  <si>
-    <t>005.mp4</t>
-  </si>
-  <si>
-    <t>I am live, come say hi</t>
-  </si>
-  <si>
-    <t>go 10136</t>
-  </si>
-  <si>
-    <t>006.mp4</t>
-  </si>
-  <si>
-    <t>Live now, all welcome</t>
-  </si>
-  <si>
-    <t>I am live, welcome</t>
-  </si>
-  <si>
-    <t>go 10137</t>
-  </si>
-  <si>
-    <t>007.mp4</t>
-  </si>
-  <si>
-    <t>Going live, hop in</t>
-  </si>
-  <si>
-    <t>Live session in progress</t>
-  </si>
-  <si>
-    <t>go 10138</t>
-  </si>
-  <si>
-    <t>008.mp4</t>
-  </si>
-  <si>
-    <t>I am live, join the fun</t>
-  </si>
-  <si>
-    <t>Streaming live, join now</t>
-  </si>
-  <si>
-    <t>go 10139</t>
-  </si>
-  <si>
-    <t>009.mp4</t>
-  </si>
-  <si>
-    <t>Live stream is live now</t>
-  </si>
-  <si>
-    <t>Live now, feel free to comment</t>
-  </si>
-  <si>
-    <t>go 10140</t>
-  </si>
-  <si>
-    <t>010.mp4</t>
-  </si>
-  <si>
-    <t>go 10141</t>
-  </si>
-  <si>
-    <t>011.mp4</t>
-  </si>
-  <si>
-    <t>go 10142</t>
-  </si>
-  <si>
-    <t>012.mp4</t>
-  </si>
-  <si>
-    <t>go 10143</t>
-  </si>
-  <si>
-    <t>013.mp4</t>
-  </si>
-  <si>
-    <t>I am live, ready to chat</t>
-  </si>
-  <si>
-    <t>Live now, come hang out</t>
-  </si>
-  <si>
-    <t>go 10144</t>
-  </si>
-  <si>
-    <t>014.mp4</t>
-  </si>
-  <si>
-    <t>go 10145</t>
-  </si>
-  <si>
-    <t>015.mp4</t>
-  </si>
-  <si>
-    <t>go 10148</t>
-  </si>
-  <si>
-    <t>018.mp4</t>
-  </si>
-  <si>
-    <t>go 10149</t>
-  </si>
-  <si>
-    <t>019.mp4</t>
-  </si>
-  <si>
-    <t>go 10150</t>
-  </si>
-  <si>
-    <t>020.mp4</t>
-  </si>
-  <si>
-    <t>go 10151</t>
-  </si>
-  <si>
-    <t>021.mp4</t>
-  </si>
-  <si>
-    <t>go 10152</t>
-  </si>
-  <si>
-    <t>022.mp4</t>
-  </si>
-  <si>
-    <t>go 10153</t>
-  </si>
-  <si>
-    <t>go 10154</t>
-  </si>
-  <si>
-    <t>024.mp4</t>
-  </si>
-  <si>
-    <t>go 10155</t>
-  </si>
-  <si>
-    <t>025.mp4</t>
-  </si>
-  <si>
-    <t>go 10156</t>
-  </si>
-  <si>
-    <t>026.mp4</t>
-  </si>
-  <si>
-    <t>go 10157</t>
-  </si>
-  <si>
-    <t>go 10158</t>
-  </si>
-  <si>
-    <t>go 10159</t>
-  </si>
-  <si>
-    <t>029.mp4</t>
-  </si>
-  <si>
-    <t>go 10160</t>
-  </si>
-  <si>
-    <t>030.mp4</t>
-  </si>
-  <si>
-    <t>go 10161</t>
-  </si>
-  <si>
-    <t>go 10162</t>
-  </si>
-  <si>
-    <t>go 10163</t>
-  </si>
-  <si>
-    <t>go 10164</t>
-  </si>
-  <si>
-    <t>034.mp4</t>
-  </si>
-  <si>
-    <t>go 10165</t>
-  </si>
-  <si>
-    <t>035.mp4</t>
-  </si>
-  <si>
-    <t>go 10166</t>
-  </si>
-  <si>
-    <t>036.mp4</t>
-  </si>
-  <si>
-    <t>go 10167</t>
-  </si>
-  <si>
-    <t>037.mp4</t>
-  </si>
-  <si>
-    <t>go 10168</t>
-  </si>
-  <si>
-    <t>038.mp4</t>
-  </si>
-  <si>
-    <t>go 10169</t>
-  </si>
-  <si>
-    <t>go 10170</t>
-  </si>
-  <si>
-    <t>040.mp4</t>
-  </si>
-  <si>
-    <t>go 10171</t>
-  </si>
-  <si>
-    <t>041.mp4</t>
-  </si>
-  <si>
-    <t>go 10172</t>
-  </si>
-  <si>
-    <t>go 10173</t>
-  </si>
-  <si>
-    <t>go 10174</t>
-  </si>
-  <si>
-    <t>044.mp4</t>
-  </si>
-  <si>
-    <t>go 10175</t>
-  </si>
-  <si>
-    <t>go 10176</t>
-  </si>
-  <si>
-    <t>046.mp4</t>
-  </si>
-  <si>
-    <t>go 10177</t>
-  </si>
-  <si>
-    <t>go 10178</t>
-  </si>
-  <si>
-    <t>048.mp4</t>
-  </si>
-  <si>
-    <t>go 10179</t>
-  </si>
-  <si>
-    <t>049.mp4</t>
-  </si>
-  <si>
-    <t>go 10180</t>
-  </si>
-  <si>
-    <t>050.mp4</t>
-  </si>
-  <si>
-    <t>go 10181</t>
-  </si>
-  <si>
-    <t>051.mp4</t>
-  </si>
-  <si>
-    <t>go 10182</t>
-  </si>
-  <si>
-    <t>052.mp4</t>
-  </si>
-  <si>
-    <t>go 10183</t>
-  </si>
-  <si>
-    <t>go 10184</t>
-  </si>
-  <si>
-    <t>go 10185</t>
-  </si>
-  <si>
-    <t>go 10186</t>
-  </si>
-  <si>
-    <t>056.mp4</t>
-  </si>
-  <si>
-    <t>go 10187</t>
-  </si>
-  <si>
-    <t>go 10188</t>
-  </si>
-  <si>
-    <t>go 10189</t>
-  </si>
-  <si>
-    <t>go 10190</t>
-  </si>
-  <si>
-    <t>go 10191</t>
-  </si>
-  <si>
-    <t>go 10192</t>
-  </si>
-  <si>
-    <t>go 10193</t>
-  </si>
-  <si>
-    <t>go 10194</t>
-  </si>
-  <si>
-    <t>go 10195</t>
-  </si>
-  <si>
-    <t>go 10196</t>
-  </si>
-  <si>
-    <t>go 10197</t>
-  </si>
-  <si>
-    <t>go 10198</t>
-  </si>
-  <si>
-    <t>go 10199</t>
-  </si>
-  <si>
-    <t>go 10200</t>
-  </si>
-  <si>
-    <t>go 10201</t>
-  </si>
-  <si>
-    <t>go 10202</t>
-  </si>
-  <si>
-    <t>go 10203</t>
-  </si>
-  <si>
-    <t>go 10204</t>
-  </si>
-  <si>
-    <t>go 10205</t>
-  </si>
-  <si>
-    <t>go 10206</t>
-  </si>
-  <si>
-    <t>go 10207</t>
-  </si>
-  <si>
-    <t>go 10208</t>
-  </si>
-  <si>
-    <t>go 10209</t>
-  </si>
-  <si>
-    <t>go 10210</t>
-  </si>
-  <si>
-    <t>go 10211</t>
-  </si>
-  <si>
-    <t>go 10212</t>
-  </si>
-  <si>
-    <t>go 10213</t>
   </si>
   <si>
     <t>go 10214</t>
@@ -2634,7 +2601,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E193"/>
+  <dimension ref="A1:E182"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <sheetData>
     <row r="1" spans="1:5">
@@ -2656,7 +2623,7 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2">
-        <v>32546</v>
+        <v>32835</v>
       </c>
       <c r="B2" t="s">
         <v>5</v>
@@ -2673,7 +2640,7 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3">
-        <v>32654</v>
+        <v>32636</v>
       </c>
       <c r="B3" t="s">
         <v>9</v>
@@ -2690,7 +2657,7 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4">
-        <v>32358</v>
+        <v>32638</v>
       </c>
       <c r="B4" t="s">
         <v>13</v>
@@ -2707,7 +2674,7 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5">
-        <v>32373</v>
+        <v>20149</v>
       </c>
       <c r="B5" t="s">
         <v>17</v>
@@ -2716,66 +2683,66 @@
         <v>18</v>
       </c>
       <c r="D5" t="s">
+        <v>8</v>
+      </c>
+      <c r="E5" t="s">
         <v>19</v>
-      </c>
-      <c r="E5" t="s">
-        <v>20</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6">
-        <v>32380</v>
+        <v>7028</v>
       </c>
       <c r="B6" t="s">
+        <v>20</v>
+      </c>
+      <c r="C6" t="s">
         <v>21</v>
       </c>
-      <c r="C6" t="s">
+      <c r="D6" t="s">
         <v>22</v>
       </c>
-      <c r="D6" t="s">
+      <c r="E6" t="s">
         <v>23</v>
-      </c>
-      <c r="E6" t="s">
-        <v>24</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7">
-        <v>32427</v>
+        <v>23504</v>
       </c>
       <c r="B7" t="s">
+        <v>24</v>
+      </c>
+      <c r="C7" t="s">
         <v>25</v>
       </c>
-      <c r="C7" t="s">
+      <c r="D7" t="s">
         <v>26</v>
       </c>
-      <c r="D7" t="s">
+      <c r="E7" t="s">
         <v>27</v>
-      </c>
-      <c r="E7" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8">
-        <v>32927</v>
+        <v>33065</v>
       </c>
       <c r="B8" t="s">
+        <v>28</v>
+      </c>
+      <c r="C8" t="s">
         <v>29</v>
       </c>
-      <c r="C8" t="s">
+      <c r="D8" t="s">
         <v>30</v>
       </c>
-      <c r="D8" t="s">
+      <c r="E8" t="s">
         <v>31</v>
-      </c>
-      <c r="E8" t="s">
-        <v>27</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9">
-        <v>33024</v>
+        <v>17255</v>
       </c>
       <c r="B9" t="s">
         <v>32</v>
@@ -2792,7 +2759,7 @@
     </row>
     <row r="10" spans="1:5">
       <c r="A10">
-        <v>33025</v>
+        <v>32362</v>
       </c>
       <c r="B10" t="s">
         <v>36</v>
@@ -2809,7 +2776,7 @@
     </row>
     <row r="11" spans="1:5">
       <c r="A11">
-        <v>33107</v>
+        <v>23470</v>
       </c>
       <c r="B11" t="s">
         <v>40</v>
@@ -2826,7 +2793,7 @@
     </row>
     <row r="12" spans="1:5">
       <c r="A12">
-        <v>32741</v>
+        <v>22291</v>
       </c>
       <c r="B12" t="s">
         <v>44</v>
@@ -2843,7 +2810,7 @@
     </row>
     <row r="13" spans="1:5">
       <c r="A13">
-        <v>32835</v>
+        <v>23404</v>
       </c>
       <c r="B13" t="s">
         <v>48</v>
@@ -2860,7 +2827,7 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14">
-        <v>32636</v>
+        <v>32532</v>
       </c>
       <c r="B14" t="s">
         <v>52</v>
@@ -2877,7 +2844,7 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15">
-        <v>32638</v>
+        <v>7065</v>
       </c>
       <c r="B15" t="s">
         <v>56</v>
@@ -2894,7 +2861,7 @@
     </row>
     <row r="16" spans="1:5">
       <c r="A16">
-        <v>20149</v>
+        <v>22302</v>
       </c>
       <c r="B16" t="s">
         <v>60</v>
@@ -2903,253 +2870,253 @@
         <v>61</v>
       </c>
       <c r="D16" t="s">
-        <v>51</v>
+        <v>62</v>
       </c>
       <c r="E16" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17">
-        <v>7028</v>
+        <v>22305</v>
       </c>
       <c r="B17" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C17" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D17" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E17" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18">
-        <v>23504</v>
+        <v>16077</v>
       </c>
       <c r="B18" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C18" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D18" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E18" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19">
-        <v>33065</v>
+        <v>22296</v>
       </c>
       <c r="B19" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C19" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D19" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E19" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20">
-        <v>17255</v>
+        <v>32703</v>
       </c>
       <c r="B20" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C20" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D20" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E20" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21">
-        <v>32362</v>
+        <v>23831</v>
       </c>
       <c r="B21" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C21" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D21" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E21" t="s">
-        <v>34</v>
+        <v>83</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22">
-        <v>23470</v>
+        <v>32397</v>
       </c>
       <c r="B22" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C22" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="D22" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="E22" t="s">
-        <v>85</v>
+        <v>11</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23">
-        <v>22291</v>
+        <v>33123</v>
       </c>
       <c r="B23" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C23" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D23" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E23" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24">
-        <v>23404</v>
+        <v>32428</v>
       </c>
       <c r="B24" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C24" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D24" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E24" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25">
-        <v>32532</v>
+        <v>22300</v>
       </c>
       <c r="B25" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C25" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D25" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E25" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26">
-        <v>7065</v>
+        <v>22295</v>
       </c>
       <c r="B26" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C26" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D26" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E26" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27">
-        <v>22302</v>
+        <v>22297</v>
       </c>
       <c r="B27" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C27" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D27" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="E27" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="A28">
-        <v>22305</v>
+        <v>23759</v>
       </c>
       <c r="B28" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C28" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D28" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E28" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29">
-        <v>16077</v>
+        <v>23723</v>
       </c>
       <c r="B29" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C29" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="D29" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="E29" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="30" spans="1:5">
       <c r="A30">
-        <v>22296</v>
+        <v>23690</v>
       </c>
       <c r="B30" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C30" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D30" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="E30" t="s">
-        <v>117</v>
+        <v>105</v>
       </c>
     </row>
     <row r="31" spans="1:5">
       <c r="A31">
-        <v>32703</v>
+        <v>16137</v>
       </c>
       <c r="B31" t="s">
         <v>118</v>
@@ -3166,7 +3133,7 @@
     </row>
     <row r="32" spans="1:5">
       <c r="A32">
-        <v>23831</v>
+        <v>22210</v>
       </c>
       <c r="B32" t="s">
         <v>122</v>
@@ -3183,7 +3150,7 @@
     </row>
     <row r="33" spans="1:5">
       <c r="A33">
-        <v>32397</v>
+        <v>16508</v>
       </c>
       <c r="B33" t="s">
         <v>126</v>
@@ -3195,63 +3162,63 @@
         <v>128</v>
       </c>
       <c r="E33" t="s">
-        <v>54</v>
+        <v>129</v>
       </c>
     </row>
     <row r="34" spans="1:5">
       <c r="A34">
-        <v>33123</v>
+        <v>16401</v>
       </c>
       <c r="B34" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C34" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="D34" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E34" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
     </row>
     <row r="35" spans="1:5">
       <c r="A35">
-        <v>32428</v>
+        <v>16334</v>
       </c>
       <c r="B35" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C35" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D35" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E35" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
     </row>
     <row r="36" spans="1:5">
       <c r="A36">
-        <v>22300</v>
+        <v>20829</v>
       </c>
       <c r="B36" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C36" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D36" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="E36" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
     </row>
     <row r="37" spans="1:5">
       <c r="A37">
-        <v>22295</v>
+        <v>17289</v>
       </c>
       <c r="B37" t="s">
         <v>141</v>
@@ -3263,29 +3230,29 @@
         <v>143</v>
       </c>
       <c r="E37" t="s">
-        <v>144</v>
+        <v>137</v>
       </c>
     </row>
     <row r="38" spans="1:5">
       <c r="A38">
-        <v>22297</v>
+        <v>17245</v>
       </c>
       <c r="B38" t="s">
+        <v>144</v>
+      </c>
+      <c r="C38" t="s">
         <v>145</v>
       </c>
-      <c r="C38" t="s">
+      <c r="D38" t="s">
         <v>146</v>
       </c>
-      <c r="D38" t="s">
+      <c r="E38" t="s">
         <v>147</v>
-      </c>
-      <c r="E38" t="s">
-        <v>20</v>
       </c>
     </row>
     <row r="39" spans="1:5">
       <c r="A39">
-        <v>23759</v>
+        <v>17247</v>
       </c>
       <c r="B39" t="s">
         <v>148</v>
@@ -3302,7 +3269,7 @@
     </row>
     <row r="40" spans="1:5">
       <c r="A40">
-        <v>23723</v>
+        <v>17111</v>
       </c>
       <c r="B40" t="s">
         <v>152</v>
@@ -3319,7 +3286,7 @@
     </row>
     <row r="41" spans="1:5">
       <c r="A41">
-        <v>23690</v>
+        <v>16492</v>
       </c>
       <c r="B41" t="s">
         <v>156</v>
@@ -3331,21 +3298,21 @@
         <v>158</v>
       </c>
       <c r="E41" t="s">
-        <v>147</v>
+        <v>159</v>
       </c>
     </row>
     <row r="42" spans="1:5">
       <c r="A42">
-        <v>16137</v>
+        <v>19774</v>
       </c>
       <c r="B42" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C42" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="D42" t="s">
-        <v>161</v>
+        <v>27</v>
       </c>
       <c r="E42" t="s">
         <v>162</v>
@@ -3353,7 +3320,7 @@
     </row>
     <row r="43" spans="1:5">
       <c r="A43">
-        <v>22210</v>
+        <v>16162</v>
       </c>
       <c r="B43" t="s">
         <v>163</v>
@@ -3370,7 +3337,7 @@
     </row>
     <row r="44" spans="1:5">
       <c r="A44">
-        <v>16508</v>
+        <v>16405</v>
       </c>
       <c r="B44" t="s">
         <v>167</v>
@@ -3387,7 +3354,7 @@
     </row>
     <row r="45" spans="1:5">
       <c r="A45">
-        <v>16401</v>
+        <v>20062</v>
       </c>
       <c r="B45" t="s">
         <v>171</v>
@@ -3404,7 +3371,7 @@
     </row>
     <row r="46" spans="1:5">
       <c r="A46">
-        <v>16334</v>
+        <v>16395</v>
       </c>
       <c r="B46" t="s">
         <v>175</v>
@@ -3421,7 +3388,7 @@
     </row>
     <row r="47" spans="1:5">
       <c r="A47">
-        <v>20829</v>
+        <v>16497</v>
       </c>
       <c r="B47" t="s">
         <v>179</v>
@@ -3430,15 +3397,15 @@
         <v>180</v>
       </c>
       <c r="D47" t="s">
+        <v>62</v>
+      </c>
+      <c r="E47" t="s">
         <v>181</v>
-      </c>
-      <c r="E47" t="s">
-        <v>174</v>
       </c>
     </row>
     <row r="48" spans="1:5">
       <c r="A48">
-        <v>17289</v>
+        <v>20194</v>
       </c>
       <c r="B48" t="s">
         <v>182</v>
@@ -3450,318 +3417,318 @@
         <v>184</v>
       </c>
       <c r="E48" t="s">
-        <v>178</v>
+        <v>185</v>
       </c>
     </row>
     <row r="49" spans="1:5">
       <c r="A49">
-        <v>17245</v>
+        <v>17240</v>
       </c>
       <c r="B49" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C49" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="D49" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="E49" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="50" spans="1:5">
       <c r="A50">
-        <v>17247</v>
+        <v>16850</v>
       </c>
       <c r="B50" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C50" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="D50" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="E50" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="51" spans="1:5">
       <c r="A51">
-        <v>17111</v>
+        <v>17659</v>
       </c>
       <c r="B51" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C51" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="D51" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="E51" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="52" spans="1:5">
       <c r="A52">
-        <v>16492</v>
+        <v>23682</v>
       </c>
       <c r="B52" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C52" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="D52" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="E52" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="53" spans="1:5">
       <c r="A53">
-        <v>19774</v>
+        <v>16507</v>
       </c>
       <c r="B53" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C53" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="D53" t="s">
-        <v>70</v>
+        <v>204</v>
       </c>
       <c r="E53" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
     </row>
     <row r="54" spans="1:5">
       <c r="A54">
-        <v>16162</v>
+        <v>16486</v>
       </c>
       <c r="B54" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="C54" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="D54" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="E54" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
     </row>
     <row r="55" spans="1:5">
       <c r="A55">
-        <v>16405</v>
+        <v>16189</v>
       </c>
       <c r="B55" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="C55" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="D55" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="E55" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
     </row>
     <row r="56" spans="1:5">
       <c r="A56">
-        <v>20062</v>
+        <v>17243</v>
       </c>
       <c r="B56" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="C56" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="D56" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="E56" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
     </row>
     <row r="57" spans="1:5">
       <c r="A57">
-        <v>16395</v>
+        <v>16917</v>
       </c>
       <c r="B57" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="C57" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="D57" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="E57" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
     </row>
     <row r="58" spans="1:5">
       <c r="A58">
-        <v>16497</v>
+        <v>17281</v>
       </c>
       <c r="B58" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="C58" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="D58" t="s">
-        <v>104</v>
+        <v>224</v>
       </c>
       <c r="E58" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
     </row>
     <row r="59" spans="1:5">
       <c r="A59">
-        <v>20194</v>
+        <v>23498</v>
       </c>
       <c r="B59" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="C59" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="D59" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="E59" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
     </row>
     <row r="60" spans="1:5">
       <c r="A60">
-        <v>17240</v>
+        <v>23518</v>
       </c>
       <c r="B60" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="C60" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="D60" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="E60" t="s">
-        <v>230</v>
+        <v>71</v>
       </c>
     </row>
     <row r="61" spans="1:5">
       <c r="A61">
-        <v>16850</v>
+        <v>20021</v>
       </c>
       <c r="B61" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="C61" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="D61" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="E61" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="62" spans="1:5">
       <c r="A62">
-        <v>17659</v>
+        <v>16141</v>
       </c>
       <c r="B62" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="C62" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="D62" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="E62" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
     </row>
     <row r="63" spans="1:5">
       <c r="A63">
-        <v>23682</v>
+        <v>17541</v>
       </c>
       <c r="B63" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="C63" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="D63" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="E63" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
     </row>
     <row r="64" spans="1:5">
       <c r="A64">
-        <v>16507</v>
+        <v>17263</v>
       </c>
       <c r="B64" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="C64" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="D64" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="E64" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
     </row>
     <row r="65" spans="1:5">
       <c r="A65">
-        <v>16486</v>
+        <v>16266</v>
       </c>
       <c r="B65" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="C65" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="D65" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="E65" t="s">
-        <v>250</v>
+        <v>150</v>
       </c>
     </row>
     <row r="66" spans="1:5">
       <c r="A66">
-        <v>16189</v>
+        <v>23371</v>
       </c>
       <c r="B66" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="C66" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D66" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E66" t="s">
-        <v>254</v>
+        <v>106</v>
       </c>
     </row>
     <row r="67" spans="1:5">
       <c r="A67">
-        <v>17243</v>
+        <v>23668</v>
       </c>
       <c r="B67" t="s">
         <v>255</v>
@@ -3778,7 +3745,7 @@
     </row>
     <row r="68" spans="1:5">
       <c r="A68">
-        <v>16917</v>
+        <v>18680</v>
       </c>
       <c r="B68" t="s">
         <v>259</v>
@@ -3795,7 +3762,7 @@
     </row>
     <row r="69" spans="1:5">
       <c r="A69">
-        <v>17281</v>
+        <v>23857</v>
       </c>
       <c r="B69" t="s">
         <v>263</v>
@@ -3804,695 +3771,695 @@
         <v>264</v>
       </c>
       <c r="D69" t="s">
-        <v>7</v>
+        <v>265</v>
       </c>
       <c r="E69" t="s">
-        <v>8</v>
+        <v>266</v>
       </c>
     </row>
     <row r="70" spans="1:5">
       <c r="A70">
-        <v>23498</v>
+        <v>7045</v>
       </c>
       <c r="B70" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="C70" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="D70" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="E70" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
     </row>
     <row r="71" spans="1:5">
       <c r="A71">
-        <v>23518</v>
+        <v>32655</v>
       </c>
       <c r="B71" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="C71" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="D71" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="E71" t="s">
-        <v>113</v>
+        <v>274</v>
       </c>
     </row>
     <row r="72" spans="1:5">
       <c r="A72">
-        <v>20021</v>
+        <v>23792</v>
       </c>
       <c r="B72" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="C72" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="D72" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="E72" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
     </row>
     <row r="73" spans="1:5">
       <c r="A73">
-        <v>16141</v>
+        <v>21942</v>
       </c>
       <c r="B73" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="C73" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="D73" t="s">
-        <v>11</v>
+        <v>281</v>
       </c>
       <c r="E73" t="s">
-        <v>12</v>
+        <v>282</v>
       </c>
     </row>
     <row r="74" spans="1:5">
       <c r="A74">
-        <v>17541</v>
+        <v>23692</v>
       </c>
       <c r="B74" t="s">
-        <v>278</v>
+        <v>283</v>
       </c>
       <c r="C74" t="s">
-        <v>279</v>
+        <v>284</v>
       </c>
       <c r="D74" t="s">
-        <v>15</v>
+        <v>285</v>
       </c>
       <c r="E74" t="s">
-        <v>16</v>
+        <v>286</v>
       </c>
     </row>
     <row r="75" spans="1:5">
       <c r="A75">
-        <v>17263</v>
+        <v>23687</v>
       </c>
       <c r="B75" t="s">
-        <v>280</v>
+        <v>287</v>
       </c>
       <c r="C75" t="s">
-        <v>281</v>
+        <v>288</v>
       </c>
       <c r="D75" t="s">
-        <v>282</v>
+        <v>289</v>
       </c>
       <c r="E75" t="s">
-        <v>283</v>
+        <v>290</v>
       </c>
     </row>
     <row r="76" spans="1:5">
       <c r="A76">
-        <v>16266</v>
+        <v>21930</v>
       </c>
       <c r="B76" t="s">
-        <v>284</v>
+        <v>291</v>
       </c>
       <c r="C76" t="s">
-        <v>285</v>
+        <v>292</v>
       </c>
       <c r="D76" t="s">
-        <v>286</v>
+        <v>39</v>
       </c>
       <c r="E76" t="s">
-        <v>191</v>
+        <v>293</v>
       </c>
     </row>
     <row r="77" spans="1:5">
       <c r="A77">
-        <v>23371</v>
+        <v>23767</v>
       </c>
       <c r="B77" t="s">
-        <v>287</v>
+        <v>294</v>
       </c>
       <c r="C77" t="s">
-        <v>288</v>
+        <v>295</v>
       </c>
       <c r="D77" t="s">
-        <v>19</v>
+        <v>296</v>
       </c>
       <c r="E77" t="s">
-        <v>20</v>
+        <v>297</v>
       </c>
     </row>
     <row r="78" spans="1:5">
       <c r="A78">
-        <v>23668</v>
+        <v>23728</v>
       </c>
       <c r="B78" t="s">
-        <v>289</v>
+        <v>298</v>
       </c>
       <c r="C78" t="s">
-        <v>290</v>
+        <v>299</v>
       </c>
       <c r="D78" t="s">
-        <v>23</v>
+        <v>300</v>
       </c>
       <c r="E78" t="s">
-        <v>24</v>
+        <v>301</v>
       </c>
     </row>
     <row r="79" spans="1:5">
       <c r="A79">
-        <v>18680</v>
+        <v>16186</v>
       </c>
       <c r="B79" t="s">
-        <v>291</v>
+        <v>302</v>
       </c>
       <c r="C79" t="s">
-        <v>292</v>
+        <v>303</v>
       </c>
       <c r="D79" t="s">
-        <v>27</v>
+        <v>304</v>
       </c>
       <c r="E79" t="s">
-        <v>28</v>
+        <v>305</v>
       </c>
     </row>
     <row r="80" spans="1:5">
       <c r="A80">
-        <v>23857</v>
+        <v>23864</v>
       </c>
       <c r="B80" t="s">
-        <v>293</v>
+        <v>306</v>
       </c>
       <c r="C80" t="s">
-        <v>294</v>
+        <v>307</v>
       </c>
       <c r="D80" t="s">
-        <v>295</v>
+        <v>308</v>
       </c>
       <c r="E80" t="s">
-        <v>296</v>
+        <v>309</v>
       </c>
     </row>
     <row r="81" spans="1:5">
       <c r="A81">
-        <v>7045</v>
+        <v>23699</v>
       </c>
       <c r="B81" t="s">
-        <v>297</v>
+        <v>310</v>
       </c>
       <c r="C81" t="s">
-        <v>298</v>
+        <v>311</v>
       </c>
       <c r="D81" t="s">
-        <v>299</v>
+        <v>312</v>
       </c>
       <c r="E81" t="s">
-        <v>300</v>
+        <v>313</v>
       </c>
     </row>
     <row r="82" spans="1:5">
       <c r="A82">
-        <v>32655</v>
+        <v>21954</v>
       </c>
       <c r="B82" t="s">
-        <v>301</v>
+        <v>314</v>
       </c>
       <c r="C82" t="s">
-        <v>302</v>
+        <v>315</v>
       </c>
       <c r="D82" t="s">
-        <v>303</v>
+        <v>316</v>
       </c>
       <c r="E82" t="s">
-        <v>304</v>
+        <v>312</v>
       </c>
     </row>
     <row r="83" spans="1:5">
       <c r="A83">
-        <v>23792</v>
+        <v>18228</v>
       </c>
       <c r="B83" t="s">
-        <v>305</v>
+        <v>317</v>
       </c>
       <c r="C83" t="s">
-        <v>306</v>
+        <v>318</v>
       </c>
       <c r="D83" t="s">
-        <v>307</v>
+        <v>319</v>
       </c>
       <c r="E83" t="s">
-        <v>308</v>
+        <v>320</v>
       </c>
     </row>
     <row r="84" spans="1:5">
       <c r="A84">
-        <v>21942</v>
+        <v>32393</v>
       </c>
       <c r="B84" t="s">
-        <v>309</v>
+        <v>321</v>
       </c>
       <c r="C84" t="s">
-        <v>310</v>
+        <v>322</v>
       </c>
       <c r="D84" t="s">
-        <v>311</v>
+        <v>323</v>
       </c>
       <c r="E84" t="s">
-        <v>312</v>
+        <v>324</v>
       </c>
     </row>
     <row r="85" spans="1:5">
       <c r="A85">
-        <v>23692</v>
+        <v>17106</v>
       </c>
       <c r="B85" t="s">
-        <v>313</v>
+        <v>325</v>
       </c>
       <c r="C85" t="s">
-        <v>314</v>
+        <v>326</v>
       </c>
       <c r="D85" t="s">
-        <v>315</v>
+        <v>327</v>
       </c>
       <c r="E85" t="s">
-        <v>316</v>
+        <v>328</v>
       </c>
     </row>
     <row r="86" spans="1:5">
       <c r="A86">
-        <v>23687</v>
+        <v>23770</v>
       </c>
       <c r="B86" t="s">
-        <v>317</v>
+        <v>329</v>
       </c>
       <c r="C86" t="s">
-        <v>318</v>
+        <v>330</v>
       </c>
       <c r="D86" t="s">
-        <v>319</v>
+        <v>331</v>
       </c>
       <c r="E86" t="s">
-        <v>320</v>
+        <v>332</v>
       </c>
     </row>
     <row r="87" spans="1:5">
       <c r="A87">
-        <v>21930</v>
+        <v>23442</v>
       </c>
       <c r="B87" t="s">
-        <v>321</v>
+        <v>333</v>
       </c>
       <c r="C87" t="s">
-        <v>322</v>
+        <v>334</v>
       </c>
       <c r="D87" t="s">
-        <v>34</v>
+        <v>7</v>
       </c>
       <c r="E87" t="s">
-        <v>35</v>
+        <v>8</v>
       </c>
     </row>
     <row r="88" spans="1:5">
       <c r="A88">
-        <v>23767</v>
+        <v>23736</v>
       </c>
       <c r="B88" t="s">
-        <v>323</v>
+        <v>335</v>
       </c>
       <c r="C88" t="s">
-        <v>324</v>
+        <v>336</v>
       </c>
       <c r="D88" t="s">
-        <v>38</v>
+        <v>11</v>
       </c>
       <c r="E88" t="s">
-        <v>39</v>
+        <v>12</v>
       </c>
     </row>
     <row r="89" spans="1:5">
       <c r="A89">
-        <v>23728</v>
+        <v>23741</v>
       </c>
       <c r="B89" t="s">
-        <v>325</v>
+        <v>337</v>
       </c>
       <c r="C89" t="s">
-        <v>326</v>
+        <v>338</v>
       </c>
       <c r="D89" t="s">
-        <v>327</v>
+        <v>15</v>
       </c>
       <c r="E89" t="s">
-        <v>328</v>
+        <v>16</v>
       </c>
     </row>
     <row r="90" spans="1:5">
       <c r="A90">
-        <v>16186</v>
+        <v>20720</v>
       </c>
       <c r="B90" t="s">
-        <v>329</v>
+        <v>339</v>
       </c>
       <c r="C90" t="s">
-        <v>330</v>
+        <v>340</v>
       </c>
       <c r="D90" t="s">
-        <v>42</v>
+        <v>341</v>
       </c>
       <c r="E90" t="s">
-        <v>43</v>
+        <v>342</v>
       </c>
     </row>
     <row r="91" spans="1:5">
       <c r="A91">
-        <v>23864</v>
+        <v>20732</v>
       </c>
       <c r="B91" t="s">
-        <v>331</v>
+        <v>343</v>
       </c>
       <c r="C91" t="s">
-        <v>332</v>
+        <v>344</v>
       </c>
       <c r="D91" t="s">
-        <v>333</v>
+        <v>8</v>
       </c>
       <c r="E91" t="s">
-        <v>334</v>
+        <v>19</v>
       </c>
     </row>
     <row r="92" spans="1:5">
       <c r="A92">
-        <v>23699</v>
+        <v>21886</v>
       </c>
       <c r="B92" t="s">
-        <v>335</v>
+        <v>345</v>
       </c>
       <c r="C92" t="s">
-        <v>336</v>
+        <v>346</v>
       </c>
       <c r="D92" t="s">
-        <v>46</v>
+        <v>22</v>
       </c>
       <c r="E92" t="s">
-        <v>47</v>
+        <v>23</v>
       </c>
     </row>
     <row r="93" spans="1:5">
       <c r="A93">
-        <v>21954</v>
+        <v>23450</v>
       </c>
       <c r="B93" t="s">
-        <v>337</v>
+        <v>347</v>
       </c>
       <c r="C93" t="s">
-        <v>338</v>
+        <v>348</v>
       </c>
       <c r="D93" t="s">
-        <v>339</v>
+        <v>34</v>
       </c>
       <c r="E93" t="s">
-        <v>46</v>
+        <v>35</v>
       </c>
     </row>
     <row r="94" spans="1:5">
       <c r="A94">
-        <v>18228</v>
+        <v>20758</v>
       </c>
       <c r="B94" t="s">
-        <v>340</v>
+        <v>349</v>
       </c>
       <c r="C94" t="s">
-        <v>341</v>
+        <v>350</v>
       </c>
       <c r="D94" t="s">
-        <v>342</v>
+        <v>38</v>
       </c>
       <c r="E94" t="s">
-        <v>343</v>
+        <v>39</v>
       </c>
     </row>
     <row r="95" spans="1:5">
       <c r="A95">
-        <v>32393</v>
+        <v>20716</v>
       </c>
       <c r="B95" t="s">
-        <v>344</v>
+        <v>351</v>
       </c>
       <c r="C95" t="s">
-        <v>345</v>
+        <v>352</v>
       </c>
       <c r="D95" t="s">
-        <v>346</v>
+        <v>42</v>
       </c>
       <c r="E95" t="s">
-        <v>347</v>
+        <v>43</v>
       </c>
     </row>
     <row r="96" spans="1:5">
       <c r="A96">
-        <v>17106</v>
+        <v>23796</v>
       </c>
       <c r="B96" t="s">
-        <v>348</v>
+        <v>353</v>
       </c>
       <c r="C96" t="s">
-        <v>349</v>
+        <v>354</v>
       </c>
       <c r="D96" t="s">
-        <v>350</v>
+        <v>46</v>
       </c>
       <c r="E96" t="s">
-        <v>351</v>
+        <v>47</v>
       </c>
     </row>
     <row r="97" spans="1:5">
       <c r="A97">
-        <v>23770</v>
+        <v>21883</v>
       </c>
       <c r="B97" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="C97" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="D97" t="s">
-        <v>354</v>
+        <v>50</v>
       </c>
       <c r="E97" t="s">
-        <v>355</v>
+        <v>51</v>
       </c>
     </row>
     <row r="98" spans="1:5">
       <c r="A98">
-        <v>23442</v>
+        <v>32823</v>
       </c>
       <c r="B98" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="C98" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="D98" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="E98" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
     </row>
     <row r="99" spans="1:5">
       <c r="A99">
-        <v>23736</v>
+        <v>20759</v>
       </c>
       <c r="B99" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="C99" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="D99" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="E99" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
     </row>
     <row r="100" spans="1:5">
       <c r="A100">
-        <v>23741</v>
+        <v>21892</v>
       </c>
       <c r="B100" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="C100" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="D100" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="E100" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
     </row>
     <row r="101" spans="1:5">
       <c r="A101">
-        <v>20720</v>
+        <v>23502</v>
       </c>
       <c r="B101" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="C101" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="D101" t="s">
-        <v>364</v>
+        <v>66</v>
       </c>
       <c r="E101" t="s">
-        <v>365</v>
+        <v>67</v>
       </c>
     </row>
     <row r="102" spans="1:5">
       <c r="A102">
-        <v>20732</v>
+        <v>23491</v>
       </c>
       <c r="B102" t="s">
+        <v>365</v>
+      </c>
+      <c r="C102" t="s">
         <v>366</v>
       </c>
-      <c r="C102" t="s">
-        <v>367</v>
-      </c>
       <c r="D102" t="s">
-        <v>51</v>
+        <v>70</v>
       </c>
       <c r="E102" t="s">
-        <v>62</v>
+        <v>71</v>
       </c>
     </row>
     <row r="103" spans="1:5">
       <c r="A103">
-        <v>21886</v>
+        <v>23524</v>
       </c>
       <c r="B103" t="s">
+        <v>367</v>
+      </c>
+      <c r="C103" t="s">
         <v>368</v>
       </c>
-      <c r="C103" t="s">
-        <v>369</v>
-      </c>
       <c r="D103" t="s">
-        <v>65</v>
+        <v>74</v>
       </c>
       <c r="E103" t="s">
-        <v>66</v>
+        <v>75</v>
       </c>
     </row>
     <row r="104" spans="1:5">
       <c r="A104">
-        <v>23450</v>
+        <v>23444</v>
       </c>
       <c r="B104" t="s">
+        <v>369</v>
+      </c>
+      <c r="C104" t="s">
         <v>370</v>
       </c>
-      <c r="C104" t="s">
-        <v>371</v>
-      </c>
       <c r="D104" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E104" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="105" spans="1:5">
       <c r="A105">
-        <v>20758</v>
+        <v>22052</v>
       </c>
       <c r="B105" t="s">
+        <v>371</v>
+      </c>
+      <c r="C105" t="s">
         <v>372</v>
       </c>
-      <c r="C105" t="s">
-        <v>373</v>
-      </c>
       <c r="D105" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E105" t="s">
-        <v>34</v>
+        <v>83</v>
       </c>
     </row>
     <row r="106" spans="1:5">
       <c r="A106">
-        <v>20716</v>
+        <v>23860</v>
       </c>
       <c r="B106" t="s">
+        <v>373</v>
+      </c>
+      <c r="C106" t="s">
         <v>374</v>
       </c>
-      <c r="C106" t="s">
-        <v>375</v>
-      </c>
       <c r="D106" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="E106" t="s">
-        <v>85</v>
+        <v>11</v>
       </c>
     </row>
     <row r="107" spans="1:5">
       <c r="A107">
-        <v>23796</v>
+        <v>23863</v>
       </c>
       <c r="B107" t="s">
+        <v>375</v>
+      </c>
+      <c r="C107" t="s">
         <v>376</v>
       </c>
-      <c r="C107" t="s">
-        <v>377</v>
-      </c>
       <c r="D107" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E107" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="108" spans="1:5">
       <c r="A108">
-        <v>21883</v>
+        <v>16411</v>
       </c>
       <c r="B108" t="s">
+        <v>377</v>
+      </c>
+      <c r="C108" t="s">
         <v>378</v>
       </c>
-      <c r="C108" t="s">
-        <v>379</v>
-      </c>
       <c r="D108" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E108" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="109" spans="1:5">
       <c r="A109">
-        <v>32823</v>
+        <v>16094</v>
       </c>
       <c r="B109" t="s">
+        <v>379</v>
+      </c>
+      <c r="C109" t="s">
         <v>380</v>
       </c>
-      <c r="C109" t="s">
-        <v>6</v>
-      </c>
       <c r="D109" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E109" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="110" spans="1:5">
       <c r="A110">
-        <v>20759</v>
+        <v>16098</v>
       </c>
       <c r="B110" t="s">
         <v>381</v>
@@ -4501,15 +4468,15 @@
         <v>382</v>
       </c>
       <c r="D110" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E110" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="111" spans="1:5">
       <c r="A111">
-        <v>21892</v>
+        <v>7047</v>
       </c>
       <c r="B111" t="s">
         <v>383</v>
@@ -4518,15 +4485,15 @@
         <v>384</v>
       </c>
       <c r="D111" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="E111" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="112" spans="1:5">
       <c r="A112">
-        <v>23502</v>
+        <v>21934</v>
       </c>
       <c r="B112" t="s">
         <v>385</v>
@@ -4535,55 +4502,55 @@
         <v>386</v>
       </c>
       <c r="D112" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E112" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="113" spans="1:5">
       <c r="A113">
-        <v>23491</v>
+        <v>20733</v>
       </c>
       <c r="B113" t="s">
         <v>387</v>
       </c>
       <c r="C113" t="s">
-        <v>10</v>
+        <v>388</v>
       </c>
       <c r="D113" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="E113" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="114" spans="1:5">
       <c r="A114">
-        <v>23524</v>
+        <v>20769</v>
       </c>
       <c r="B114" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="C114" t="s">
-        <v>14</v>
+        <v>390</v>
       </c>
       <c r="D114" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="E114" t="s">
-        <v>117</v>
+        <v>105</v>
       </c>
     </row>
     <row r="115" spans="1:5">
       <c r="A115">
-        <v>23444</v>
+        <v>20560</v>
       </c>
       <c r="B115" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="C115" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="D115" t="s">
         <v>120</v>
@@ -4594,13 +4561,13 @@
     </row>
     <row r="116" spans="1:5">
       <c r="A116">
-        <v>22052</v>
+        <v>23779</v>
       </c>
       <c r="B116" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="C116" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="D116" t="s">
         <v>124</v>
@@ -4611,115 +4578,115 @@
     </row>
     <row r="117" spans="1:5">
       <c r="A117">
-        <v>23860</v>
+        <v>23781</v>
       </c>
       <c r="B117" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="C117" t="s">
-        <v>18</v>
+        <v>396</v>
       </c>
       <c r="D117" t="s">
         <v>128</v>
       </c>
       <c r="E117" t="s">
-        <v>54</v>
+        <v>129</v>
       </c>
     </row>
     <row r="118" spans="1:5">
       <c r="A118">
-        <v>23863</v>
+        <v>22292</v>
       </c>
       <c r="B118" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="C118" t="s">
-        <v>22</v>
+        <v>398</v>
       </c>
       <c r="D118" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E118" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
     </row>
     <row r="119" spans="1:5">
       <c r="A119">
-        <v>16411</v>
+        <v>22320</v>
       </c>
       <c r="B119" t="s">
-        <v>395</v>
+        <v>399</v>
       </c>
       <c r="C119" t="s">
-        <v>26</v>
+        <v>400</v>
       </c>
       <c r="D119" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E119" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
     </row>
     <row r="120" spans="1:5">
       <c r="A120">
-        <v>16094</v>
+        <v>23411</v>
       </c>
       <c r="B120" t="s">
-        <v>396</v>
+        <v>401</v>
       </c>
       <c r="C120" t="s">
-        <v>397</v>
+        <v>402</v>
       </c>
       <c r="D120" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="E120" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
     </row>
     <row r="121" spans="1:5">
       <c r="A121">
-        <v>16098</v>
+        <v>23415</v>
       </c>
       <c r="B121" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="C121" t="s">
-        <v>399</v>
+        <v>404</v>
       </c>
       <c r="D121" t="s">
         <v>143</v>
       </c>
       <c r="E121" t="s">
-        <v>144</v>
+        <v>137</v>
       </c>
     </row>
     <row r="122" spans="1:5">
       <c r="A122">
-        <v>7047</v>
+        <v>23419</v>
       </c>
       <c r="B122" t="s">
-        <v>400</v>
+        <v>405</v>
       </c>
       <c r="C122" t="s">
-        <v>401</v>
+        <v>406</v>
       </c>
       <c r="D122" t="s">
+        <v>146</v>
+      </c>
+      <c r="E122" t="s">
         <v>147</v>
-      </c>
-      <c r="E122" t="s">
-        <v>20</v>
       </c>
     </row>
     <row r="123" spans="1:5">
       <c r="A123">
-        <v>21934</v>
+        <v>23420</v>
       </c>
       <c r="B123" t="s">
-        <v>402</v>
+        <v>407</v>
       </c>
       <c r="C123" t="s">
-        <v>403</v>
+        <v>408</v>
       </c>
       <c r="D123" t="s">
         <v>150</v>
@@ -4730,13 +4697,13 @@
     </row>
     <row r="124" spans="1:5">
       <c r="A124">
-        <v>20733</v>
+        <v>23733</v>
       </c>
       <c r="B124" t="s">
-        <v>404</v>
+        <v>409</v>
       </c>
       <c r="C124" t="s">
-        <v>405</v>
+        <v>410</v>
       </c>
       <c r="D124" t="s">
         <v>154</v>
@@ -4747,33 +4714,33 @@
     </row>
     <row r="125" spans="1:5">
       <c r="A125">
-        <v>20769</v>
+        <v>23734</v>
       </c>
       <c r="B125" t="s">
-        <v>406</v>
+        <v>411</v>
       </c>
       <c r="C125" t="s">
-        <v>30</v>
+        <v>412</v>
       </c>
       <c r="D125" t="s">
         <v>158</v>
       </c>
       <c r="E125" t="s">
-        <v>147</v>
+        <v>159</v>
       </c>
     </row>
     <row r="126" spans="1:5">
       <c r="A126">
-        <v>20560</v>
+        <v>23745</v>
       </c>
       <c r="B126" t="s">
-        <v>407</v>
+        <v>413</v>
       </c>
       <c r="C126" t="s">
-        <v>408</v>
+        <v>414</v>
       </c>
       <c r="D126" t="s">
-        <v>161</v>
+        <v>27</v>
       </c>
       <c r="E126" t="s">
         <v>162</v>
@@ -4781,13 +4748,13 @@
     </row>
     <row r="127" spans="1:5">
       <c r="A127">
-        <v>23779</v>
+        <v>23757</v>
       </c>
       <c r="B127" t="s">
-        <v>409</v>
+        <v>415</v>
       </c>
       <c r="C127" t="s">
-        <v>410</v>
+        <v>416</v>
       </c>
       <c r="D127" t="s">
         <v>165</v>
@@ -4798,13 +4765,13 @@
     </row>
     <row r="128" spans="1:5">
       <c r="A128">
-        <v>23781</v>
+        <v>23735</v>
       </c>
       <c r="B128" t="s">
-        <v>411</v>
+        <v>417</v>
       </c>
       <c r="C128" t="s">
-        <v>33</v>
+        <v>6</v>
       </c>
       <c r="D128" t="s">
         <v>169</v>
@@ -4815,13 +4782,13 @@
     </row>
     <row r="129" spans="1:5">
       <c r="A129">
-        <v>22292</v>
+        <v>23737</v>
       </c>
       <c r="B129" t="s">
-        <v>412</v>
+        <v>418</v>
       </c>
       <c r="C129" t="s">
-        <v>37</v>
+        <v>10</v>
       </c>
       <c r="D129" t="s">
         <v>173</v>
@@ -4832,13 +4799,13 @@
     </row>
     <row r="130" spans="1:5">
       <c r="A130">
-        <v>22320</v>
+        <v>23744</v>
       </c>
       <c r="B130" t="s">
-        <v>413</v>
+        <v>419</v>
       </c>
       <c r="C130" t="s">
-        <v>414</v>
+        <v>14</v>
       </c>
       <c r="D130" t="s">
         <v>177</v>
@@ -4849,353 +4816,353 @@
     </row>
     <row r="131" spans="1:5">
       <c r="A131">
-        <v>23411</v>
+        <v>23742</v>
       </c>
       <c r="B131" t="s">
-        <v>415</v>
+        <v>420</v>
       </c>
       <c r="C131" t="s">
-        <v>41</v>
+        <v>421</v>
       </c>
       <c r="D131" t="s">
+        <v>62</v>
+      </c>
+      <c r="E131" t="s">
         <v>181</v>
-      </c>
-      <c r="E131" t="s">
-        <v>174</v>
       </c>
     </row>
     <row r="132" spans="1:5">
       <c r="A132">
-        <v>23415</v>
+        <v>23740</v>
       </c>
       <c r="B132" t="s">
-        <v>416</v>
+        <v>422</v>
       </c>
       <c r="C132" t="s">
-        <v>417</v>
+        <v>18</v>
       </c>
       <c r="D132" t="s">
         <v>184</v>
       </c>
       <c r="E132" t="s">
-        <v>178</v>
+        <v>185</v>
       </c>
     </row>
     <row r="133" spans="1:5">
       <c r="A133">
-        <v>23419</v>
+        <v>23729</v>
       </c>
       <c r="B133" t="s">
-        <v>418</v>
+        <v>423</v>
       </c>
       <c r="C133" t="s">
-        <v>45</v>
+        <v>21</v>
       </c>
       <c r="D133" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="E133" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="134" spans="1:5">
       <c r="A134">
-        <v>23420</v>
+        <v>23727</v>
       </c>
       <c r="B134" t="s">
-        <v>419</v>
+        <v>424</v>
       </c>
       <c r="C134" t="s">
-        <v>420</v>
+        <v>25</v>
       </c>
       <c r="D134" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="E134" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="135" spans="1:5">
       <c r="A135">
-        <v>23733</v>
+        <v>23715</v>
       </c>
       <c r="B135" t="s">
-        <v>421</v>
+        <v>425</v>
       </c>
       <c r="C135" t="s">
-        <v>422</v>
+        <v>29</v>
       </c>
       <c r="D135" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="E135" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="136" spans="1:5">
       <c r="A136">
-        <v>23734</v>
+        <v>23713</v>
       </c>
       <c r="B136" t="s">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c r="C136" t="s">
-        <v>424</v>
+        <v>33</v>
       </c>
       <c r="D136" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="E136" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="137" spans="1:5">
       <c r="A137">
-        <v>23745</v>
+        <v>23711</v>
       </c>
       <c r="B137" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="C137" t="s">
-        <v>426</v>
+        <v>37</v>
       </c>
       <c r="D137" t="s">
-        <v>70</v>
+        <v>204</v>
       </c>
       <c r="E137" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
     </row>
     <row r="138" spans="1:5">
       <c r="A138">
-        <v>23757</v>
+        <v>23706</v>
       </c>
       <c r="B138" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="C138" t="s">
-        <v>428</v>
+        <v>41</v>
       </c>
       <c r="D138" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="E138" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
     </row>
     <row r="139" spans="1:5">
       <c r="A139">
-        <v>23735</v>
+        <v>23705</v>
       </c>
       <c r="B139" t="s">
         <v>429</v>
       </c>
       <c r="C139" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="D139" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="E139" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
     </row>
     <row r="140" spans="1:5">
       <c r="A140">
-        <v>23737</v>
+        <v>23697</v>
       </c>
       <c r="B140" t="s">
         <v>430</v>
       </c>
       <c r="C140" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="D140" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="E140" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
     </row>
     <row r="141" spans="1:5">
       <c r="A141">
-        <v>23744</v>
+        <v>23696</v>
       </c>
       <c r="B141" t="s">
         <v>431</v>
       </c>
       <c r="C141" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="D141" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="E141" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
     </row>
     <row r="142" spans="1:5">
       <c r="A142">
-        <v>23742</v>
+        <v>23685</v>
       </c>
       <c r="B142" t="s">
         <v>432</v>
       </c>
       <c r="C142" t="s">
-        <v>433</v>
+        <v>57</v>
       </c>
       <c r="D142" t="s">
-        <v>104</v>
+        <v>224</v>
       </c>
       <c r="E142" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
     </row>
     <row r="143" spans="1:5">
       <c r="A143">
-        <v>23740</v>
+        <v>23500</v>
       </c>
       <c r="B143" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="C143" t="s">
         <v>61</v>
       </c>
       <c r="D143" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="E143" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
     </row>
     <row r="144" spans="1:5">
       <c r="A144">
-        <v>23729</v>
+        <v>23554</v>
       </c>
       <c r="B144" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="C144" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D144" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="E144" t="s">
-        <v>230</v>
+        <v>71</v>
       </c>
     </row>
     <row r="145" spans="1:5">
       <c r="A145">
-        <v>23727</v>
+        <v>23565</v>
       </c>
       <c r="B145" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="C145" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D145" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="E145" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="146" spans="1:5">
       <c r="A146">
-        <v>23715</v>
+        <v>23574</v>
       </c>
       <c r="B146" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="C146" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D146" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="E146" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
     </row>
     <row r="147" spans="1:5">
       <c r="A147">
-        <v>23713</v>
+        <v>23598</v>
       </c>
       <c r="B147" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="C147" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D147" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="E147" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
     </row>
     <row r="148" spans="1:5">
       <c r="A148">
-        <v>23711</v>
+        <v>23607</v>
       </c>
       <c r="B148" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="C148" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D148" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="E148" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
     </row>
     <row r="149" spans="1:5">
       <c r="A149">
-        <v>23706</v>
+        <v>23636</v>
       </c>
       <c r="B149" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="C149" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="D149" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="E149" t="s">
-        <v>250</v>
+        <v>150</v>
       </c>
     </row>
     <row r="150" spans="1:5">
       <c r="A150">
-        <v>23705</v>
+        <v>23641</v>
       </c>
       <c r="B150" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="C150" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D150" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E150" t="s">
-        <v>254</v>
+        <v>106</v>
       </c>
     </row>
     <row r="151" spans="1:5">
       <c r="A151">
-        <v>23697</v>
+        <v>23643</v>
       </c>
       <c r="B151" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="C151" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D151" t="s">
         <v>257</v>
@@ -5206,13 +5173,13 @@
     </row>
     <row r="152" spans="1:5">
       <c r="A152">
-        <v>23696</v>
+        <v>23658</v>
       </c>
       <c r="B152" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="C152" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D152" t="s">
         <v>261</v>
@@ -5223,109 +5190,109 @@
     </row>
     <row r="153" spans="1:5">
       <c r="A153">
-        <v>23685</v>
+        <v>23719</v>
       </c>
       <c r="B153" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="C153" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D153" t="s">
-        <v>7</v>
+        <v>265</v>
       </c>
       <c r="E153" t="s">
-        <v>8</v>
+        <v>266</v>
       </c>
     </row>
     <row r="154" spans="1:5">
       <c r="A154">
-        <v>23500</v>
+        <v>23709</v>
       </c>
       <c r="B154" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="C154" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D154" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="E154" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
     </row>
     <row r="155" spans="1:5">
       <c r="A155">
-        <v>23554</v>
+        <v>23700</v>
       </c>
       <c r="B155" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="C155" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D155" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="E155" t="s">
-        <v>113</v>
+        <v>274</v>
       </c>
     </row>
     <row r="156" spans="1:5">
       <c r="A156">
-        <v>23565</v>
+        <v>23675</v>
       </c>
       <c r="B156" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="C156" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="D156" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="E156" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
     </row>
     <row r="157" spans="1:5">
       <c r="A157">
-        <v>23574</v>
+        <v>23674</v>
       </c>
       <c r="B157" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="C157" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D157" t="s">
-        <v>11</v>
+        <v>281</v>
       </c>
       <c r="E157" t="s">
-        <v>12</v>
+        <v>282</v>
       </c>
     </row>
     <row r="158" spans="1:5">
       <c r="A158">
-        <v>23598</v>
+        <v>23651</v>
       </c>
       <c r="B158" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="C158" t="s">
         <v>119</v>
       </c>
       <c r="D158" t="s">
-        <v>15</v>
+        <v>449</v>
       </c>
       <c r="E158" t="s">
-        <v>16</v>
+        <v>261</v>
       </c>
     </row>
     <row r="159" spans="1:5">
       <c r="A159">
-        <v>23607</v>
+        <v>23650</v>
       </c>
       <c r="B159" t="s">
         <v>450</v>
@@ -5334,15 +5301,15 @@
         <v>123</v>
       </c>
       <c r="D159" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="E159" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
     </row>
     <row r="160" spans="1:5">
       <c r="A160">
-        <v>23636</v>
+        <v>23612</v>
       </c>
       <c r="B160" t="s">
         <v>451</v>
@@ -5351,66 +5318,66 @@
         <v>127</v>
       </c>
       <c r="D160" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="E160" t="s">
-        <v>191</v>
+        <v>290</v>
       </c>
     </row>
     <row r="161" spans="1:5">
       <c r="A161">
-        <v>23641</v>
+        <v>23590</v>
       </c>
       <c r="B161" t="s">
         <v>452</v>
       </c>
       <c r="C161" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="D161" t="s">
-        <v>19</v>
+        <v>39</v>
       </c>
       <c r="E161" t="s">
-        <v>20</v>
+        <v>293</v>
       </c>
     </row>
     <row r="162" spans="1:5">
       <c r="A162">
-        <v>23643</v>
+        <v>20671</v>
       </c>
       <c r="B162" t="s">
         <v>453</v>
       </c>
       <c r="C162" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D162" t="s">
-        <v>23</v>
+        <v>296</v>
       </c>
       <c r="E162" t="s">
-        <v>24</v>
+        <v>297</v>
       </c>
     </row>
     <row r="163" spans="1:5">
       <c r="A163">
-        <v>23658</v>
+        <v>23544</v>
       </c>
       <c r="B163" t="s">
         <v>454</v>
       </c>
       <c r="C163" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D163" t="s">
-        <v>27</v>
+        <v>300</v>
       </c>
       <c r="E163" t="s">
-        <v>28</v>
+        <v>301</v>
       </c>
     </row>
     <row r="164" spans="1:5">
       <c r="A164">
-        <v>23719</v>
+        <v>23487</v>
       </c>
       <c r="B164" t="s">
         <v>455</v>
@@ -5419,32 +5386,32 @@
         <v>142</v>
       </c>
       <c r="D164" t="s">
-        <v>295</v>
+        <v>304</v>
       </c>
       <c r="E164" t="s">
-        <v>296</v>
+        <v>305</v>
       </c>
     </row>
     <row r="165" spans="1:5">
       <c r="A165">
-        <v>23709</v>
+        <v>23483</v>
       </c>
       <c r="B165" t="s">
         <v>456</v>
       </c>
       <c r="C165" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D165" t="s">
-        <v>299</v>
+        <v>308</v>
       </c>
       <c r="E165" t="s">
-        <v>300</v>
+        <v>309</v>
       </c>
     </row>
     <row r="166" spans="1:5">
       <c r="A166">
-        <v>23700</v>
+        <v>23479</v>
       </c>
       <c r="B166" t="s">
         <v>457</v>
@@ -5453,15 +5420,15 @@
         <v>149</v>
       </c>
       <c r="D166" t="s">
-        <v>303</v>
+        <v>312</v>
       </c>
       <c r="E166" t="s">
-        <v>304</v>
+        <v>313</v>
       </c>
     </row>
     <row r="167" spans="1:5">
       <c r="A167">
-        <v>23675</v>
+        <v>23475</v>
       </c>
       <c r="B167" t="s">
         <v>458</v>
@@ -5470,15 +5437,15 @@
         <v>153</v>
       </c>
       <c r="D167" t="s">
-        <v>307</v>
+        <v>316</v>
       </c>
       <c r="E167" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
     </row>
     <row r="168" spans="1:5">
       <c r="A168">
-        <v>23674</v>
+        <v>23469</v>
       </c>
       <c r="B168" t="s">
         <v>459</v>
@@ -5487,32 +5454,32 @@
         <v>157</v>
       </c>
       <c r="D168" t="s">
-        <v>311</v>
+        <v>319</v>
       </c>
       <c r="E168" t="s">
-        <v>312</v>
+        <v>320</v>
       </c>
     </row>
     <row r="169" spans="1:5">
       <c r="A169">
-        <v>23651</v>
+        <v>23468</v>
       </c>
       <c r="B169" t="s">
         <v>460</v>
       </c>
       <c r="C169" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="D169" t="s">
-        <v>31</v>
+        <v>323</v>
       </c>
       <c r="E169" t="s">
-        <v>27</v>
+        <v>324</v>
       </c>
     </row>
     <row r="170" spans="1:5">
       <c r="A170">
-        <v>23650</v>
+        <v>23467</v>
       </c>
       <c r="B170" t="s">
         <v>461</v>
@@ -5521,15 +5488,15 @@
         <v>164</v>
       </c>
       <c r="D170" t="s">
-        <v>315</v>
+        <v>327</v>
       </c>
       <c r="E170" t="s">
-        <v>316</v>
+        <v>328</v>
       </c>
     </row>
     <row r="171" spans="1:5">
       <c r="A171">
-        <v>23612</v>
+        <v>23440</v>
       </c>
       <c r="B171" t="s">
         <v>462</v>
@@ -5538,15 +5505,15 @@
         <v>168</v>
       </c>
       <c r="D171" t="s">
-        <v>319</v>
+        <v>331</v>
       </c>
       <c r="E171" t="s">
-        <v>320</v>
+        <v>332</v>
       </c>
     </row>
     <row r="172" spans="1:5">
       <c r="A172">
-        <v>23590</v>
+        <v>23439</v>
       </c>
       <c r="B172" t="s">
         <v>463</v>
@@ -5555,15 +5522,15 @@
         <v>172</v>
       </c>
       <c r="D172" t="s">
-        <v>34</v>
+        <v>7</v>
       </c>
       <c r="E172" t="s">
-        <v>35</v>
+        <v>8</v>
       </c>
     </row>
     <row r="173" spans="1:5">
       <c r="A173">
-        <v>20671</v>
+        <v>23827</v>
       </c>
       <c r="B173" t="s">
         <v>464</v>
@@ -5572,15 +5539,15 @@
         <v>176</v>
       </c>
       <c r="D173" t="s">
-        <v>38</v>
+        <v>11</v>
       </c>
       <c r="E173" t="s">
-        <v>39</v>
+        <v>12</v>
       </c>
     </row>
     <row r="174" spans="1:5">
       <c r="A174">
-        <v>23544</v>
+        <v>23766</v>
       </c>
       <c r="B174" t="s">
         <v>465</v>
@@ -5589,15 +5556,15 @@
         <v>180</v>
       </c>
       <c r="D174" t="s">
-        <v>327</v>
+        <v>15</v>
       </c>
       <c r="E174" t="s">
-        <v>328</v>
+        <v>16</v>
       </c>
     </row>
     <row r="175" spans="1:5">
       <c r="A175">
-        <v>23487</v>
+        <v>23761</v>
       </c>
       <c r="B175" t="s">
         <v>466</v>
@@ -5606,316 +5573,129 @@
         <v>183</v>
       </c>
       <c r="D175" t="s">
-        <v>42</v>
+        <v>341</v>
       </c>
       <c r="E175" t="s">
-        <v>43</v>
+        <v>342</v>
       </c>
     </row>
     <row r="176" spans="1:5">
       <c r="A176">
-        <v>23483</v>
+        <v>23788</v>
       </c>
       <c r="B176" t="s">
         <v>467</v>
       </c>
       <c r="C176" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="D176" t="s">
-        <v>333</v>
+        <v>8</v>
       </c>
       <c r="E176" t="s">
-        <v>334</v>
+        <v>19</v>
       </c>
     </row>
     <row r="177" spans="1:5">
       <c r="A177">
-        <v>23479</v>
+        <v>23774</v>
       </c>
       <c r="B177" t="s">
         <v>468</v>
       </c>
       <c r="C177" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="D177" t="s">
-        <v>46</v>
+        <v>22</v>
       </c>
       <c r="E177" t="s">
-        <v>47</v>
+        <v>23</v>
       </c>
     </row>
     <row r="178" spans="1:5">
       <c r="A178">
-        <v>23475</v>
+        <v>23749</v>
       </c>
       <c r="B178" t="s">
         <v>469</v>
       </c>
       <c r="C178" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="D178" t="s">
-        <v>339</v>
+        <v>26</v>
       </c>
       <c r="E178" t="s">
-        <v>46</v>
+        <v>27</v>
       </c>
     </row>
     <row r="179" spans="1:5">
       <c r="A179">
-        <v>23469</v>
+        <v>23750</v>
       </c>
       <c r="B179" t="s">
         <v>470</v>
       </c>
       <c r="C179" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="D179" t="s">
-        <v>342</v>
+        <v>30</v>
       </c>
       <c r="E179" t="s">
-        <v>343</v>
+        <v>31</v>
       </c>
     </row>
     <row r="180" spans="1:5">
       <c r="A180">
-        <v>23468</v>
+        <v>23771</v>
       </c>
       <c r="B180" t="s">
         <v>471</v>
       </c>
       <c r="C180" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="D180" t="s">
-        <v>346</v>
+        <v>34</v>
       </c>
       <c r="E180" t="s">
-        <v>347</v>
+        <v>35</v>
       </c>
     </row>
     <row r="181" spans="1:5">
       <c r="A181">
-        <v>23467</v>
+        <v>23772</v>
       </c>
       <c r="B181" t="s">
         <v>472</v>
       </c>
       <c r="C181" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="D181" t="s">
-        <v>350</v>
+        <v>38</v>
       </c>
       <c r="E181" t="s">
-        <v>351</v>
+        <v>39</v>
       </c>
     </row>
     <row r="182" spans="1:5">
       <c r="A182">
-        <v>23440</v>
+        <v>23786</v>
       </c>
       <c r="B182" t="s">
         <v>473</v>
       </c>
       <c r="C182" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="D182" t="s">
-        <v>354</v>
+        <v>42</v>
       </c>
       <c r="E182" t="s">
-        <v>355</v>
-      </c>
-    </row>
-    <row r="183" spans="1:5">
-      <c r="A183">
-        <v>23439</v>
-      </c>
-      <c r="B183" t="s">
-        <v>474</v>
-      </c>
-      <c r="C183" t="s">
-        <v>213</v>
-      </c>
-      <c r="D183" t="s">
-        <v>50</v>
-      </c>
-      <c r="E183" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="184" spans="1:5">
-      <c r="A184">
-        <v>23827</v>
-      </c>
-      <c r="B184" t="s">
-        <v>475</v>
-      </c>
-      <c r="C184" t="s">
-        <v>217</v>
-      </c>
-      <c r="D184" t="s">
-        <v>54</v>
-      </c>
-      <c r="E184" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="185" spans="1:5">
-      <c r="A185">
-        <v>23766</v>
-      </c>
-      <c r="B185" t="s">
-        <v>476</v>
-      </c>
-      <c r="C185" t="s">
-        <v>221</v>
-      </c>
-      <c r="D185" t="s">
-        <v>58</v>
-      </c>
-      <c r="E185" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="186" spans="1:5">
-      <c r="A186">
-        <v>23761</v>
-      </c>
-      <c r="B186" t="s">
-        <v>477</v>
-      </c>
-      <c r="C186" t="s">
-        <v>224</v>
-      </c>
-      <c r="D186" t="s">
-        <v>364</v>
-      </c>
-      <c r="E186" t="s">
-        <v>365</v>
-      </c>
-    </row>
-    <row r="187" spans="1:5">
-      <c r="A187">
-        <v>23788</v>
-      </c>
-      <c r="B187" t="s">
-        <v>478</v>
-      </c>
-      <c r="C187" t="s">
-        <v>228</v>
-      </c>
-      <c r="D187" t="s">
-        <v>51</v>
-      </c>
-      <c r="E187" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="188" spans="1:5">
-      <c r="A188">
-        <v>23774</v>
-      </c>
-      <c r="B188" t="s">
-        <v>479</v>
-      </c>
-      <c r="C188" t="s">
-        <v>232</v>
-      </c>
-      <c r="D188" t="s">
-        <v>65</v>
-      </c>
-      <c r="E188" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="189" spans="1:5">
-      <c r="A189">
-        <v>23749</v>
-      </c>
-      <c r="B189" t="s">
-        <v>480</v>
-      </c>
-      <c r="C189" t="s">
-        <v>236</v>
-      </c>
-      <c r="D189" t="s">
-        <v>69</v>
-      </c>
-      <c r="E189" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="190" spans="1:5">
-      <c r="A190">
-        <v>23750</v>
-      </c>
-      <c r="B190" t="s">
-        <v>481</v>
-      </c>
-      <c r="C190" t="s">
-        <v>240</v>
-      </c>
-      <c r="D190" t="s">
-        <v>73</v>
-      </c>
-      <c r="E190" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="191" spans="1:5">
-      <c r="A191">
-        <v>23771</v>
-      </c>
-      <c r="B191" t="s">
-        <v>482</v>
-      </c>
-      <c r="C191" t="s">
-        <v>244</v>
-      </c>
-      <c r="D191" t="s">
-        <v>77</v>
-      </c>
-      <c r="E191" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="192" spans="1:5">
-      <c r="A192">
-        <v>23772</v>
-      </c>
-      <c r="B192" t="s">
-        <v>483</v>
-      </c>
-      <c r="C192" t="s">
-        <v>248</v>
-      </c>
-      <c r="D192" t="s">
-        <v>81</v>
-      </c>
-      <c r="E192" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="193" spans="1:5">
-      <c r="A193">
-        <v>23786</v>
-      </c>
-      <c r="B193" t="s">
-        <v>484</v>
-      </c>
-      <c r="C193" t="s">
-        <v>252</v>
-      </c>
-      <c r="D193" t="s">
-        <v>84</v>
-      </c>
-      <c r="E193" t="s">
-        <v>85</v>
+        <v>43</v>
       </c>
     </row>
   </sheetData>
